--- a/product_upload/packages/46/file.xlsx
+++ b/product_upload/packages/46/file.xlsx
@@ -419,7 +419,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AT101"/>
+  <dimension ref="A1:AU101"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -600,7 +600,7 @@
       </c>
       <c r="AJ1" t="inlineStr">
         <is>
-          <t>Manufacture Name</t>
+          <t>Manufacturer Name</t>
         </is>
       </c>
       <c r="AK1" t="inlineStr">
@@ -649,6 +649,11 @@
         </is>
       </c>
       <c r="AT1" t="inlineStr">
+        <is>
+          <t>Name / En</t>
+        </is>
+      </c>
+      <c r="AU1" t="inlineStr">
         <is>
           <t>Seller SKU</t>
         </is>
@@ -673,7 +678,7 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Morocco</t>
+          <t>MA</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -828,6 +833,11 @@
       <c r="AS2" t="inlineStr"/>
       <c r="AT2" t="inlineStr">
         <is>
+          <t>Ribex</t>
+        </is>
+      </c>
+      <c r="AU2" t="inlineStr">
+        <is>
           <t>SKU-F6257E2D75AF</t>
         </is>
       </c>
@@ -851,7 +861,7 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Morocco</t>
+          <t>MA</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -1010,6 +1020,11 @@
       <c r="AS3" t="inlineStr"/>
       <c r="AT3" t="inlineStr">
         <is>
+          <t>CO-Ribex</t>
+        </is>
+      </c>
+      <c r="AU3" t="inlineStr">
+        <is>
           <t>SKU-BFD5D7144B35</t>
         </is>
       </c>
@@ -1033,7 +1048,7 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Morocco</t>
+          <t>MA</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -1200,6 +1215,11 @@
       </c>
       <c r="AT4" t="inlineStr">
         <is>
+          <t>CO-Ribex</t>
+        </is>
+      </c>
+      <c r="AU4" t="inlineStr">
+        <is>
           <t>SKU-B8D66FDCC0A8</t>
         </is>
       </c>
@@ -1223,7 +1243,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Morocco</t>
+          <t>MA</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -1386,6 +1406,11 @@
       <c r="AS5" t="inlineStr"/>
       <c r="AT5" t="inlineStr">
         <is>
+          <t>CO-Ribex</t>
+        </is>
+      </c>
+      <c r="AU5" t="inlineStr">
+        <is>
           <t>SKU-C8378E7E822C</t>
         </is>
       </c>
@@ -1409,7 +1434,7 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -1576,6 +1601,11 @@
       <c r="AS6" t="inlineStr"/>
       <c r="AT6" t="inlineStr">
         <is>
+          <t>Rotavex Solution</t>
+        </is>
+      </c>
+      <c r="AU6" t="inlineStr">
+        <is>
           <t>SKU-E68CBD3AD21C</t>
         </is>
       </c>
@@ -1599,7 +1629,7 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Spain</t>
+          <t>ES</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -1762,6 +1792,11 @@
       </c>
       <c r="AT7" t="inlineStr">
         <is>
+          <t>Resincalcio</t>
+        </is>
+      </c>
+      <c r="AU7" t="inlineStr">
+        <is>
           <t>SKU-F81E4B6D181B</t>
         </is>
       </c>
@@ -1785,7 +1820,7 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>India</t>
+          <t>IN</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -1958,6 +1993,11 @@
       </c>
       <c r="AT8" t="inlineStr">
         <is>
+          <t>Duserex</t>
+        </is>
+      </c>
+      <c r="AU8" t="inlineStr">
+        <is>
           <t>SKU-061F2688AC2F</t>
         </is>
       </c>
@@ -1981,7 +2021,7 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>India</t>
+          <t>IN</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -2140,6 +2180,11 @@
       <c r="AS9" t="inlineStr"/>
       <c r="AT9" t="inlineStr">
         <is>
+          <t>Glevate</t>
+        </is>
+      </c>
+      <c r="AU9" t="inlineStr">
+        <is>
           <t>SKU-7B4F6AC792E6</t>
         </is>
       </c>
@@ -2163,7 +2208,7 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -2334,6 +2379,11 @@
       </c>
       <c r="AT10" t="inlineStr">
         <is>
+          <t>Ravixa</t>
+        </is>
+      </c>
+      <c r="AU10" t="inlineStr">
+        <is>
           <t>SKU-8FA5123F8D94</t>
         </is>
       </c>
@@ -2357,7 +2407,7 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>France</t>
+          <t>FR</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -2528,6 +2578,11 @@
       </c>
       <c r="AT11" t="inlineStr">
         <is>
+          <t>Basaglar Tempo Pen</t>
+        </is>
+      </c>
+      <c r="AU11" t="inlineStr">
+        <is>
           <t>SKU-37ECC2B5E8D8</t>
         </is>
       </c>
@@ -2551,7 +2606,7 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>France</t>
+          <t>FR</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -2714,6 +2769,11 @@
       <c r="AS12" t="inlineStr"/>
       <c r="AT12" t="inlineStr">
         <is>
+          <t>Humalog Tempo Pen</t>
+        </is>
+      </c>
+      <c r="AU12" t="inlineStr">
+        <is>
           <t>SKU-F07071917E28</t>
         </is>
       </c>
@@ -2737,7 +2797,7 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Poland</t>
+          <t>PL</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -2898,6 +2958,11 @@
       <c r="AS13" t="inlineStr"/>
       <c r="AT13" t="inlineStr">
         <is>
+          <t>FANCATA 100MG TABLET</t>
+        </is>
+      </c>
+      <c r="AU13" t="inlineStr">
+        <is>
           <t>SKU-546B2960F90D</t>
         </is>
       </c>
@@ -2921,7 +2986,7 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Poland</t>
+          <t>PL</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -3090,6 +3155,11 @@
       </c>
       <c r="AT14" t="inlineStr">
         <is>
+          <t>FANCATA 50MG TABLET</t>
+        </is>
+      </c>
+      <c r="AU14" t="inlineStr">
+        <is>
           <t>SKU-62B7BF785701</t>
         </is>
       </c>
@@ -3113,7 +3183,7 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Czech Republic</t>
+          <t>CZ</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -3284,6 +3354,11 @@
       </c>
       <c r="AT15" t="inlineStr">
         <is>
+          <t>MOBIXEN</t>
+        </is>
+      </c>
+      <c r="AU15" t="inlineStr">
+        <is>
           <t>SKU-0AF60ECBFC2A</t>
         </is>
       </c>
@@ -3307,7 +3382,7 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -3478,6 +3553,11 @@
       </c>
       <c r="AT16" t="inlineStr">
         <is>
+          <t>BRIMOCOM</t>
+        </is>
+      </c>
+      <c r="AU16" t="inlineStr">
+        <is>
           <t>SKU-4975B93C56AD</t>
         </is>
       </c>
@@ -3501,7 +3581,7 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Netherlands</t>
+          <t>NL</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -3664,6 +3744,11 @@
       <c r="AS17" t="inlineStr"/>
       <c r="AT17" t="inlineStr">
         <is>
+          <t>NOXAFIL</t>
+        </is>
+      </c>
+      <c r="AU17" t="inlineStr">
+        <is>
           <t>SKU-692D05DB2D34</t>
         </is>
       </c>
@@ -3687,7 +3772,7 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>United Arab Emirates</t>
+          <t>AE</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -3850,6 +3935,11 @@
       <c r="AS18" t="inlineStr"/>
       <c r="AT18" t="inlineStr">
         <is>
+          <t xml:space="preserve">Irma-HCT 150 mg / 12.5 mg </t>
+        </is>
+      </c>
+      <c r="AU18" t="inlineStr">
+        <is>
           <t>SKU-C06C253D64DE</t>
         </is>
       </c>
@@ -3873,7 +3963,7 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>United Arab Emirates</t>
+          <t>AE</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -4040,6 +4130,11 @@
       </c>
       <c r="AT19" t="inlineStr">
         <is>
+          <t>IRMA-HCT 300 mg / 12.5 mg</t>
+        </is>
+      </c>
+      <c r="AU19" t="inlineStr">
+        <is>
           <t>SKU-DFBBD75A45C9</t>
         </is>
       </c>
@@ -4063,7 +4158,7 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>United Arab Emirates</t>
+          <t>AE</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -4226,6 +4321,11 @@
       </c>
       <c r="AT20" t="inlineStr">
         <is>
+          <t>ADOL</t>
+        </is>
+      </c>
+      <c r="AU20" t="inlineStr">
+        <is>
           <t>SKU-4EFB63148B11</t>
         </is>
       </c>
@@ -4249,7 +4349,7 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>United Arab Emirates</t>
+          <t>AE</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -4408,6 +4508,11 @@
       <c r="AS21" t="inlineStr"/>
       <c r="AT21" t="inlineStr">
         <is>
+          <t>ADOL</t>
+        </is>
+      </c>
+      <c r="AU21" t="inlineStr">
+        <is>
           <t>SKU-22450C8F4AAA</t>
         </is>
       </c>
@@ -4431,7 +4536,7 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>United Arab Emirates</t>
+          <t>AE</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -4594,6 +4699,11 @@
       <c r="AS22" t="inlineStr"/>
       <c r="AT22" t="inlineStr">
         <is>
+          <t>ADOL</t>
+        </is>
+      </c>
+      <c r="AU22" t="inlineStr">
+        <is>
           <t>SKU-205FB7939A3C</t>
         </is>
       </c>
@@ -4617,7 +4727,7 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Poland</t>
+          <t>PL</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -4786,6 +4896,11 @@
       </c>
       <c r="AT23" t="inlineStr">
         <is>
+          <t>VIDONORM 5MG/4MG TABLET</t>
+        </is>
+      </c>
+      <c r="AU23" t="inlineStr">
+        <is>
           <t>SKU-379AD8E07A91</t>
         </is>
       </c>
@@ -4809,7 +4924,7 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Poland</t>
+          <t>PL</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -4978,6 +5093,11 @@
       </c>
       <c r="AT24" t="inlineStr">
         <is>
+          <t>VIDONORM 5MG/8MG TABLET</t>
+        </is>
+      </c>
+      <c r="AU24" t="inlineStr">
+        <is>
           <t>SKU-6390E81E67D5</t>
         </is>
       </c>
@@ -5001,7 +5121,7 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Poland</t>
+          <t>PL</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -5170,6 +5290,11 @@
       </c>
       <c r="AT25" t="inlineStr">
         <is>
+          <t>VIDONORM 10MG/4MG TABLET</t>
+        </is>
+      </c>
+      <c r="AU25" t="inlineStr">
+        <is>
           <t>SKU-AB1246D5293E</t>
         </is>
       </c>
@@ -5193,7 +5318,7 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Poland</t>
+          <t>PL</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -5354,6 +5479,11 @@
       <c r="AS26" t="inlineStr"/>
       <c r="AT26" t="inlineStr">
         <is>
+          <t>VIDONORM 10MG/8MG TABLET</t>
+        </is>
+      </c>
+      <c r="AU26" t="inlineStr">
+        <is>
           <t>SKU-580D04294CB6</t>
         </is>
       </c>
@@ -5377,7 +5507,7 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -5548,6 +5678,11 @@
       <c r="AS27" t="inlineStr"/>
       <c r="AT27" t="inlineStr">
         <is>
+          <t>LORINASE-D</t>
+        </is>
+      </c>
+      <c r="AU27" t="inlineStr">
+        <is>
           <t>SKU-9E23F30D365B</t>
         </is>
       </c>
@@ -5571,7 +5706,7 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>India</t>
+          <t>IN</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -5740,6 +5875,11 @@
       <c r="AS28" t="inlineStr"/>
       <c r="AT28" t="inlineStr">
         <is>
+          <t>Metolina</t>
+        </is>
+      </c>
+      <c r="AU28" t="inlineStr">
+        <is>
           <t>SKU-F8222DB712BD</t>
         </is>
       </c>
@@ -5763,7 +5903,7 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Italy</t>
+          <t>IT</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -5934,6 +6074,11 @@
       <c r="AS29" t="inlineStr"/>
       <c r="AT29" t="inlineStr">
         <is>
+          <t>Trimbow</t>
+        </is>
+      </c>
+      <c r="AU29" t="inlineStr">
+        <is>
           <t>SKU-344AFE2163AF</t>
         </is>
       </c>
@@ -5957,7 +6102,7 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Greece</t>
+          <t>GR</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -6126,6 +6271,11 @@
       <c r="AS30" t="inlineStr"/>
       <c r="AT30" t="inlineStr">
         <is>
+          <t>Palipra</t>
+        </is>
+      </c>
+      <c r="AU30" t="inlineStr">
+        <is>
           <t>SKU-674C439C0E17</t>
         </is>
       </c>
@@ -6149,7 +6299,7 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Greece</t>
+          <t>GR</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -6318,6 +6468,11 @@
       <c r="AS31" t="inlineStr"/>
       <c r="AT31" t="inlineStr">
         <is>
+          <t>Palipra</t>
+        </is>
+      </c>
+      <c r="AU31" t="inlineStr">
+        <is>
           <t>SKU-6629B0C14DBF</t>
         </is>
       </c>
@@ -6341,7 +6496,7 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Slovenia</t>
+          <t>SI</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -6500,6 +6655,11 @@
       <c r="AS32" t="inlineStr"/>
       <c r="AT32" t="inlineStr">
         <is>
+          <t>Aryzalera</t>
+        </is>
+      </c>
+      <c r="AU32" t="inlineStr">
+        <is>
           <t>SKU-5A81BCC6F935</t>
         </is>
       </c>
@@ -6523,7 +6683,7 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Slovenia</t>
+          <t>SI</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -6686,6 +6846,11 @@
       <c r="AS33" t="inlineStr"/>
       <c r="AT33" t="inlineStr">
         <is>
+          <t>Aryzalera</t>
+        </is>
+      </c>
+      <c r="AU33" t="inlineStr">
+        <is>
           <t>SKU-D75D00B33A3A</t>
         </is>
       </c>
@@ -6709,7 +6874,7 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -6872,6 +7037,11 @@
       <c r="AS34" t="inlineStr"/>
       <c r="AT34" t="inlineStr">
         <is>
+          <t>Olcontro</t>
+        </is>
+      </c>
+      <c r="AU34" t="inlineStr">
+        <is>
           <t>SKU-014DBD1811C6</t>
         </is>
       </c>
@@ -6895,7 +7065,7 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -7062,6 +7232,11 @@
       </c>
       <c r="AT35" t="inlineStr">
         <is>
+          <t>Olcontro</t>
+        </is>
+      </c>
+      <c r="AU35" t="inlineStr">
+        <is>
           <t>SKU-07E4F61B92F2</t>
         </is>
       </c>
@@ -7085,7 +7260,7 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Egypt</t>
+          <t>EG</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -7250,6 +7425,11 @@
       </c>
       <c r="AT36" t="inlineStr">
         <is>
+          <t>Attencare</t>
+        </is>
+      </c>
+      <c r="AU36" t="inlineStr">
+        <is>
           <t>SKU-88394521C8C9</t>
         </is>
       </c>
@@ -7273,7 +7453,7 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Egypt</t>
+          <t>EG</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -7434,6 +7614,11 @@
       <c r="AS37" t="inlineStr"/>
       <c r="AT37" t="inlineStr">
         <is>
+          <t>Attencare</t>
+        </is>
+      </c>
+      <c r="AU37" t="inlineStr">
+        <is>
           <t>SKU-8FC7371CFE29</t>
         </is>
       </c>
@@ -7457,7 +7642,7 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Egypt</t>
+          <t>EG</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -7622,6 +7807,11 @@
       </c>
       <c r="AT38" t="inlineStr">
         <is>
+          <t>Attencare</t>
+        </is>
+      </c>
+      <c r="AU38" t="inlineStr">
+        <is>
           <t>SKU-230B81C6353A</t>
         </is>
       </c>
@@ -7645,7 +7835,7 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Egypt</t>
+          <t>EG</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -7806,6 +7996,11 @@
       <c r="AS39" t="inlineStr"/>
       <c r="AT39" t="inlineStr">
         <is>
+          <t>Attencare</t>
+        </is>
+      </c>
+      <c r="AU39" t="inlineStr">
+        <is>
           <t>SKU-8FC41883D6CF</t>
         </is>
       </c>
@@ -7829,7 +8024,7 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Egypt</t>
+          <t>EG</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -7994,6 +8189,11 @@
       </c>
       <c r="AT40" t="inlineStr">
         <is>
+          <t>Attencare</t>
+        </is>
+      </c>
+      <c r="AU40" t="inlineStr">
+        <is>
           <t>SKU-FFEB2473A281</t>
         </is>
       </c>
@@ -8017,7 +8217,7 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -8176,6 +8376,11 @@
       <c r="AS41" t="inlineStr"/>
       <c r="AT41" t="inlineStr">
         <is>
+          <t>Iphen</t>
+        </is>
+      </c>
+      <c r="AU41" t="inlineStr">
+        <is>
           <t>SKU-7F1FB98CA86F</t>
         </is>
       </c>
@@ -8199,7 +8404,7 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>India</t>
+          <t>IN</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -8366,6 +8571,11 @@
       <c r="AS42" t="inlineStr"/>
       <c r="AT42" t="inlineStr">
         <is>
+          <t>VALGAN</t>
+        </is>
+      </c>
+      <c r="AU42" t="inlineStr">
+        <is>
           <t>SKU-B29B73E25D5D</t>
         </is>
       </c>
@@ -8389,7 +8599,7 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -8548,6 +8758,11 @@
       <c r="AS43" t="inlineStr"/>
       <c r="AT43" t="inlineStr">
         <is>
+          <t>Vantra</t>
+        </is>
+      </c>
+      <c r="AU43" t="inlineStr">
+        <is>
           <t>SKU-30A7464B14C0</t>
         </is>
       </c>
@@ -8571,7 +8786,7 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -8726,6 +8941,11 @@
       <c r="AS44" t="inlineStr"/>
       <c r="AT44" t="inlineStr">
         <is>
+          <t>Vantra</t>
+        </is>
+      </c>
+      <c r="AU44" t="inlineStr">
+        <is>
           <t>SKU-37A571DA42CA</t>
         </is>
       </c>
@@ -8749,7 +8969,7 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>India</t>
+          <t>IN</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -8920,6 +9140,11 @@
       <c r="AS45" t="inlineStr"/>
       <c r="AT45" t="inlineStr">
         <is>
+          <t>Zillion</t>
+        </is>
+      </c>
+      <c r="AU45" t="inlineStr">
+        <is>
           <t>SKU-A6549CF8F14E</t>
         </is>
       </c>
@@ -8943,7 +9168,7 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Austria</t>
+          <t>AT</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -9114,6 +9339,11 @@
       </c>
       <c r="AT46" t="inlineStr">
         <is>
+          <t>Ziextenzo</t>
+        </is>
+      </c>
+      <c r="AU46" t="inlineStr">
+        <is>
           <t>SKU-59FB1AB92CB5</t>
         </is>
       </c>
@@ -9137,7 +9367,7 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Jordan</t>
+          <t>JO</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -9296,6 +9526,11 @@
       <c r="AS47" t="inlineStr"/>
       <c r="AT47" t="inlineStr">
         <is>
+          <t>Rozitta</t>
+        </is>
+      </c>
+      <c r="AU47" t="inlineStr">
+        <is>
           <t>SKU-147FE086BD84</t>
         </is>
       </c>
@@ -9319,7 +9554,7 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Jordan</t>
+          <t>JO</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -9482,6 +9717,11 @@
       </c>
       <c r="AT48" t="inlineStr">
         <is>
+          <t>Rozitta</t>
+        </is>
+      </c>
+      <c r="AU48" t="inlineStr">
+        <is>
           <t>SKU-37EE2B433DCB</t>
         </is>
       </c>
@@ -9505,7 +9745,7 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -9676,6 +9916,11 @@
       <c r="AS49" t="inlineStr"/>
       <c r="AT49" t="inlineStr">
         <is>
+          <t xml:space="preserve">KROMAFINA </t>
+        </is>
+      </c>
+      <c r="AU49" t="inlineStr">
+        <is>
           <t>SKU-82F211CB1609</t>
         </is>
       </c>
@@ -9699,7 +9944,7 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -9870,6 +10115,11 @@
       <c r="AS50" t="inlineStr"/>
       <c r="AT50" t="inlineStr">
         <is>
+          <t>KROMAFINA</t>
+        </is>
+      </c>
+      <c r="AU50" t="inlineStr">
+        <is>
           <t>SKU-8B468453ACA5</t>
         </is>
       </c>
@@ -9893,7 +10143,7 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>India</t>
+          <t>IN</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -10068,6 +10318,11 @@
       </c>
       <c r="AT51" t="inlineStr">
         <is>
+          <t>Sphingolin</t>
+        </is>
+      </c>
+      <c r="AU51" t="inlineStr">
+        <is>
           <t>SKU-B8D50DB0EF1E</t>
         </is>
       </c>
@@ -10091,7 +10346,7 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>India</t>
+          <t>IN</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -10266,6 +10521,11 @@
       </c>
       <c r="AT52" t="inlineStr">
         <is>
+          <t>Olmevasc</t>
+        </is>
+      </c>
+      <c r="AU52" t="inlineStr">
+        <is>
           <t>SKU-4E23AFEC3020</t>
         </is>
       </c>
@@ -10289,7 +10549,7 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>India</t>
+          <t>IN</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -10460,6 +10720,11 @@
       <c r="AS53" t="inlineStr"/>
       <c r="AT53" t="inlineStr">
         <is>
+          <t>Olmevasc</t>
+        </is>
+      </c>
+      <c r="AU53" t="inlineStr">
+        <is>
           <t>SKU-806AF901E65A</t>
         </is>
       </c>
@@ -10483,7 +10748,7 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>India</t>
+          <t>IN</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -10654,6 +10919,11 @@
       <c r="AS54" t="inlineStr"/>
       <c r="AT54" t="inlineStr">
         <is>
+          <t>Olmevasc</t>
+        </is>
+      </c>
+      <c r="AU54" t="inlineStr">
+        <is>
           <t>SKU-49746B53B7AA</t>
         </is>
       </c>
@@ -10677,7 +10947,7 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>India</t>
+          <t>IN</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -10852,6 +11122,11 @@
       </c>
       <c r="AT55" t="inlineStr">
         <is>
+          <t>Olmevasc</t>
+        </is>
+      </c>
+      <c r="AU55" t="inlineStr">
+        <is>
           <t>SKU-A35D938F095E</t>
         </is>
       </c>
@@ -10875,7 +11150,7 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -11050,6 +11325,11 @@
       </c>
       <c r="AT56" t="inlineStr">
         <is>
+          <t>Cartimov</t>
+        </is>
+      </c>
+      <c r="AU56" t="inlineStr">
+        <is>
           <t>SKU-4542A160F80E</t>
         </is>
       </c>
@@ -11073,7 +11353,7 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>India</t>
+          <t>IN</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -11246,6 +11526,11 @@
       <c r="AS57" t="inlineStr"/>
       <c r="AT57" t="inlineStr">
         <is>
+          <t>Lipofirate</t>
+        </is>
+      </c>
+      <c r="AU57" t="inlineStr">
+        <is>
           <t>SKU-350625AD0DB8</t>
         </is>
       </c>
@@ -11269,7 +11554,7 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>India</t>
+          <t>IN</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
@@ -11436,6 +11721,11 @@
       <c r="AS58" t="inlineStr"/>
       <c r="AT58" t="inlineStr">
         <is>
+          <t>Telfocus</t>
+        </is>
+      </c>
+      <c r="AU58" t="inlineStr">
+        <is>
           <t>SKU-72E7F2C86FBB</t>
         </is>
       </c>
@@ -11459,7 +11749,7 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>India</t>
+          <t>IN</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
@@ -11626,6 +11916,11 @@
       <c r="AS59" t="inlineStr"/>
       <c r="AT59" t="inlineStr">
         <is>
+          <t>Telfocus</t>
+        </is>
+      </c>
+      <c r="AU59" t="inlineStr">
+        <is>
           <t>SKU-1A31489E8E84</t>
         </is>
       </c>
@@ -11649,7 +11944,7 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>India</t>
+          <t>IN</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
@@ -11820,6 +12115,11 @@
       </c>
       <c r="AT60" t="inlineStr">
         <is>
+          <t>Zapnex</t>
+        </is>
+      </c>
+      <c r="AU60" t="inlineStr">
+        <is>
           <t>SKU-E16AA2DDEA21</t>
         </is>
       </c>
@@ -11843,7 +12143,7 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>India</t>
+          <t>IN</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
@@ -12010,6 +12310,11 @@
       <c r="AS61" t="inlineStr"/>
       <c r="AT61" t="inlineStr">
         <is>
+          <t>Zapnex</t>
+        </is>
+      </c>
+      <c r="AU61" t="inlineStr">
+        <is>
           <t>SKU-4606900C88E8</t>
         </is>
       </c>
@@ -12033,7 +12338,7 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Italy</t>
+          <t>IT</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
@@ -12212,6 +12517,11 @@
       </c>
       <c r="AT62" t="inlineStr">
         <is>
+          <t>KLACID 125MG-5ML SUSP</t>
+        </is>
+      </c>
+      <c r="AU62" t="inlineStr">
+        <is>
           <t>SKU-6738A2DE93AD</t>
         </is>
       </c>
@@ -12235,7 +12545,7 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
@@ -12410,6 +12720,11 @@
       </c>
       <c r="AT63" t="inlineStr">
         <is>
+          <t>FUSIBACT-B CREAM</t>
+        </is>
+      </c>
+      <c r="AU63" t="inlineStr">
+        <is>
           <t>SKU-3E42B9127D78</t>
         </is>
       </c>
@@ -12433,7 +12748,7 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
@@ -12604,6 +12919,11 @@
       </c>
       <c r="AT64" t="inlineStr">
         <is>
+          <t>ENFORZA</t>
+        </is>
+      </c>
+      <c r="AU64" t="inlineStr">
+        <is>
           <t>SKU-22FA81448A11</t>
         </is>
       </c>
@@ -12627,7 +12947,7 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Germany</t>
+          <t>DE</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
@@ -12794,6 +13114,11 @@
       </c>
       <c r="AT65" t="inlineStr">
         <is>
+          <t>ARTELAC COMPLETE MDO EYE LUBRICANT</t>
+        </is>
+      </c>
+      <c r="AU65" t="inlineStr">
+        <is>
           <t>SKU-01DA402F73EF</t>
         </is>
       </c>
@@ -12817,7 +13142,7 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Jordan</t>
+          <t>JO</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
@@ -12984,6 +13309,11 @@
       </c>
       <c r="AT66" t="inlineStr">
         <is>
+          <t>OROTIX 120MG F.C.TABLET</t>
+        </is>
+      </c>
+      <c r="AU66" t="inlineStr">
+        <is>
           <t>SKU-AD74F7B9905C</t>
         </is>
       </c>
@@ -13007,7 +13337,7 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
@@ -13178,6 +13508,11 @@
       <c r="AS67" t="inlineStr"/>
       <c r="AT67" t="inlineStr">
         <is>
+          <t>Vittoria-HCT</t>
+        </is>
+      </c>
+      <c r="AU67" t="inlineStr">
+        <is>
           <t>SKU-C92A4F118212</t>
         </is>
       </c>
@@ -13201,7 +13536,7 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
@@ -13372,6 +13707,11 @@
       <c r="AS68" t="inlineStr"/>
       <c r="AT68" t="inlineStr">
         <is>
+          <t>Vittoria-HCT</t>
+        </is>
+      </c>
+      <c r="AU68" t="inlineStr">
+        <is>
           <t>SKU-FE318ED21483</t>
         </is>
       </c>
@@ -13395,7 +13735,7 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
@@ -13566,6 +13906,11 @@
       <c r="AS69" t="inlineStr"/>
       <c r="AT69" t="inlineStr">
         <is>
+          <t>Vittoria-HCT</t>
+        </is>
+      </c>
+      <c r="AU69" t="inlineStr">
+        <is>
           <t>SKU-A092A27D8313</t>
         </is>
       </c>
@@ -13589,7 +13934,7 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>France</t>
+          <t>FR</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
@@ -13756,6 +14101,11 @@
       </c>
       <c r="AT70" t="inlineStr">
         <is>
+          <t>Xermelo</t>
+        </is>
+      </c>
+      <c r="AU70" t="inlineStr">
+        <is>
           <t>SKU-442616C89457</t>
         </is>
       </c>
@@ -13779,7 +14129,7 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Jordan</t>
+          <t>JO</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
@@ -13938,6 +14288,11 @@
       <c r="AS71" t="inlineStr"/>
       <c r="AT71" t="inlineStr">
         <is>
+          <t>Lovista</t>
+        </is>
+      </c>
+      <c r="AU71" t="inlineStr">
+        <is>
           <t>SKU-21EA80C98563</t>
         </is>
       </c>
@@ -13961,7 +14316,7 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Jordan</t>
+          <t>JO</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
@@ -14120,6 +14475,11 @@
       <c r="AS72" t="inlineStr"/>
       <c r="AT72" t="inlineStr">
         <is>
+          <t>Lovista</t>
+        </is>
+      </c>
+      <c r="AU72" t="inlineStr">
+        <is>
           <t>SKU-0F2B366519B5</t>
         </is>
       </c>
@@ -14143,7 +14503,7 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Germany</t>
+          <t>DE</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
@@ -14310,6 +14670,11 @@
       </c>
       <c r="AT73" t="inlineStr">
         <is>
+          <t>Vimpat</t>
+        </is>
+      </c>
+      <c r="AU73" t="inlineStr">
+        <is>
           <t>SKU-9FF51189A2DC</t>
         </is>
       </c>
@@ -14333,7 +14698,7 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
@@ -14500,6 +14865,11 @@
       <c r="AS74" t="inlineStr"/>
       <c r="AT74" t="inlineStr">
         <is>
+          <t>Adijet</t>
+        </is>
+      </c>
+      <c r="AU74" t="inlineStr">
+        <is>
           <t>SKU-54D076870EEC</t>
         </is>
       </c>
@@ -14523,7 +14893,7 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
@@ -14694,6 +15064,11 @@
       </c>
       <c r="AT75" t="inlineStr">
         <is>
+          <t>Vedoxin</t>
+        </is>
+      </c>
+      <c r="AU75" t="inlineStr">
+        <is>
           <t>SKU-27D11DB2EB04</t>
         </is>
       </c>
@@ -14717,7 +15092,7 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
@@ -14884,6 +15259,11 @@
       <c r="AS76" t="inlineStr"/>
       <c r="AT76" t="inlineStr">
         <is>
+          <t>Vedoxin</t>
+        </is>
+      </c>
+      <c r="AU76" t="inlineStr">
+        <is>
           <t>SKU-A99C4AC70B2A</t>
         </is>
       </c>
@@ -14907,7 +15287,7 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
@@ -15066,6 +15446,11 @@
       <c r="AS77" t="inlineStr"/>
       <c r="AT77" t="inlineStr">
         <is>
+          <t>Minoxil</t>
+        </is>
+      </c>
+      <c r="AU77" t="inlineStr">
+        <is>
           <t>SKU-CEF241E459FF</t>
         </is>
       </c>
@@ -15089,7 +15474,7 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Ireland</t>
+          <t>IE</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
@@ -15260,6 +15645,11 @@
       </c>
       <c r="AT78" t="inlineStr">
         <is>
+          <t>Dona</t>
+        </is>
+      </c>
+      <c r="AU78" t="inlineStr">
+        <is>
           <t>SKU-1AB37652CA4B</t>
         </is>
       </c>
@@ -15283,7 +15673,7 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Denmark</t>
+          <t>DK</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
@@ -15454,6 +15844,11 @@
       <c r="AS79" t="inlineStr"/>
       <c r="AT79" t="inlineStr">
         <is>
+          <t>Rybelsus</t>
+        </is>
+      </c>
+      <c r="AU79" t="inlineStr">
+        <is>
           <t>SKU-1D497BA6419D</t>
         </is>
       </c>
@@ -15477,7 +15872,7 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Denmark</t>
+          <t>DK</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
@@ -15648,6 +16043,11 @@
       <c r="AS80" t="inlineStr"/>
       <c r="AT80" t="inlineStr">
         <is>
+          <t>Rybelsus</t>
+        </is>
+      </c>
+      <c r="AU80" t="inlineStr">
+        <is>
           <t>SKU-6F2480B6F3EA</t>
         </is>
       </c>
@@ -15671,7 +16071,7 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Denmark</t>
+          <t>DK</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
@@ -15846,6 +16246,11 @@
       <c r="AS81" t="inlineStr"/>
       <c r="AT81" t="inlineStr">
         <is>
+          <t>Rybelsus</t>
+        </is>
+      </c>
+      <c r="AU81" t="inlineStr">
+        <is>
           <t>SKU-E4243C0F48A0</t>
         </is>
       </c>
@@ -15869,7 +16274,7 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Denmark</t>
+          <t>DK</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
@@ -16036,6 +16441,11 @@
       <c r="AS82" t="inlineStr"/>
       <c r="AT82" t="inlineStr">
         <is>
+          <t>Rybelsus</t>
+        </is>
+      </c>
+      <c r="AU82" t="inlineStr">
+        <is>
           <t>SKU-DD256B72E3CB</t>
         </is>
       </c>
@@ -16059,7 +16469,7 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Denmark</t>
+          <t>DK</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
@@ -16222,6 +16632,11 @@
       <c r="AS83" t="inlineStr"/>
       <c r="AT83" t="inlineStr">
         <is>
+          <t>Rybelsus</t>
+        </is>
+      </c>
+      <c r="AU83" t="inlineStr">
+        <is>
           <t>SKU-B1C7DCC9A157</t>
         </is>
       </c>
@@ -16245,7 +16660,7 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Denmark</t>
+          <t>DK</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
@@ -16416,6 +16831,11 @@
       </c>
       <c r="AT84" t="inlineStr">
         <is>
+          <t>Rybelsus</t>
+        </is>
+      </c>
+      <c r="AU84" t="inlineStr">
+        <is>
           <t>SKU-8013098A7497</t>
         </is>
       </c>
@@ -16439,7 +16859,7 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>India</t>
+          <t>IN</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
@@ -16602,6 +17022,11 @@
       </c>
       <c r="AT85" t="inlineStr">
         <is>
+          <t>Bosfit</t>
+        </is>
+      </c>
+      <c r="AU85" t="inlineStr">
+        <is>
           <t>SKU-7D92E2B03AC7</t>
         </is>
       </c>
@@ -16625,7 +17050,7 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>India</t>
+          <t>IN</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
@@ -16800,6 +17225,11 @@
       </c>
       <c r="AT86" t="inlineStr">
         <is>
+          <t>ESOPOLE</t>
+        </is>
+      </c>
+      <c r="AU86" t="inlineStr">
+        <is>
           <t>SKU-10F09205A637</t>
         </is>
       </c>
@@ -16823,7 +17253,7 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>India</t>
+          <t>IN</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
@@ -16986,6 +17416,11 @@
       <c r="AS87" t="inlineStr"/>
       <c r="AT87" t="inlineStr">
         <is>
+          <t>ESOPOLE</t>
+        </is>
+      </c>
+      <c r="AU87" t="inlineStr">
+        <is>
           <t>SKU-7419B1A80A1E</t>
         </is>
       </c>
@@ -17009,7 +17444,7 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>India</t>
+          <t>IN</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
@@ -17184,6 +17619,11 @@
       </c>
       <c r="AT88" t="inlineStr">
         <is>
+          <t>ESOPOLE</t>
+        </is>
+      </c>
+      <c r="AU88" t="inlineStr">
+        <is>
           <t>SKU-624D792611B8</t>
         </is>
       </c>
@@ -17207,7 +17647,7 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>India</t>
+          <t>IN</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
@@ -17382,6 +17822,11 @@
       </c>
       <c r="AT89" t="inlineStr">
         <is>
+          <t>ESOPOLE</t>
+        </is>
+      </c>
+      <c r="AU89" t="inlineStr">
+        <is>
           <t>SKU-96F6B631D369</t>
         </is>
       </c>
@@ -17405,7 +17850,7 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>India</t>
+          <t>IN</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
@@ -17576,6 +18021,11 @@
       <c r="AS90" t="inlineStr"/>
       <c r="AT90" t="inlineStr">
         <is>
+          <t>ESOPOLE</t>
+        </is>
+      </c>
+      <c r="AU90" t="inlineStr">
+        <is>
           <t>SKU-1AA4BCD41BB4</t>
         </is>
       </c>
@@ -17599,7 +18049,7 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>India</t>
+          <t>IN</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
@@ -17770,6 +18220,11 @@
       <c r="AS91" t="inlineStr"/>
       <c r="AT91" t="inlineStr">
         <is>
+          <t>ESOPOLE</t>
+        </is>
+      </c>
+      <c r="AU91" t="inlineStr">
+        <is>
           <t>SKU-182582FA66BF</t>
         </is>
       </c>
@@ -17793,7 +18248,7 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Egypt</t>
+          <t>EG</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
@@ -17958,6 +18413,11 @@
       </c>
       <c r="AT92" t="inlineStr">
         <is>
+          <t>Erastapecs Co</t>
+        </is>
+      </c>
+      <c r="AU92" t="inlineStr">
+        <is>
           <t>SKU-B745B6174CD6</t>
         </is>
       </c>
@@ -17981,7 +18441,7 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Egypt</t>
+          <t>EG</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
@@ -18142,6 +18602,11 @@
       <c r="AS93" t="inlineStr"/>
       <c r="AT93" t="inlineStr">
         <is>
+          <t>Erastapecs Co</t>
+        </is>
+      </c>
+      <c r="AU93" t="inlineStr">
+        <is>
           <t>SKU-71C4A6C6C2DB</t>
         </is>
       </c>
@@ -18165,7 +18630,7 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Egypt</t>
+          <t>EG</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
@@ -18326,6 +18791,11 @@
       <c r="AS94" t="inlineStr"/>
       <c r="AT94" t="inlineStr">
         <is>
+          <t>Erastapecs Co</t>
+        </is>
+      </c>
+      <c r="AU94" t="inlineStr">
+        <is>
           <t>SKU-5DE503A6BB5B</t>
         </is>
       </c>
@@ -18349,7 +18819,7 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Spain</t>
+          <t>ES</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
@@ -18512,6 +18982,11 @@
       <c r="AS95" t="inlineStr"/>
       <c r="AT95" t="inlineStr">
         <is>
+          <t>TEBARAT</t>
+        </is>
+      </c>
+      <c r="AU95" t="inlineStr">
+        <is>
           <t>SKU-DD9DD9154A19</t>
         </is>
       </c>
@@ -18535,7 +19010,7 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
@@ -18694,6 +19169,11 @@
       <c r="AS96" t="inlineStr"/>
       <c r="AT96" t="inlineStr">
         <is>
+          <t>Coxinix</t>
+        </is>
+      </c>
+      <c r="AU96" t="inlineStr">
+        <is>
           <t>SKU-EE587D9FA867</t>
         </is>
       </c>
@@ -18717,7 +19197,7 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Jordan</t>
+          <t>JO</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
@@ -18890,6 +19370,11 @@
       </c>
       <c r="AT97" t="inlineStr">
         <is>
+          <t>Poliza</t>
+        </is>
+      </c>
+      <c r="AU97" t="inlineStr">
+        <is>
           <t>SKU-75AE07807253</t>
         </is>
       </c>
@@ -18913,7 +19398,7 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Jordan</t>
+          <t>JO</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
@@ -19086,6 +19571,11 @@
       </c>
       <c r="AT98" t="inlineStr">
         <is>
+          <t>Poliza</t>
+        </is>
+      </c>
+      <c r="AU98" t="inlineStr">
+        <is>
           <t>SKU-7EB9BA5505C7</t>
         </is>
       </c>
@@ -19109,7 +19599,7 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>US</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
@@ -19276,6 +19766,11 @@
       <c r="AS99" t="inlineStr"/>
       <c r="AT99" t="inlineStr">
         <is>
+          <t>Abrilada</t>
+        </is>
+      </c>
+      <c r="AU99" t="inlineStr">
+        <is>
           <t>SKU-129C510B24F5</t>
         </is>
       </c>
@@ -19299,7 +19794,7 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>US</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
@@ -19474,6 +19969,11 @@
       <c r="AS100" t="inlineStr"/>
       <c r="AT100" t="inlineStr">
         <is>
+          <t>Abrilada</t>
+        </is>
+      </c>
+      <c r="AU100" t="inlineStr">
+        <is>
           <t>SKU-328A7B455F8C</t>
         </is>
       </c>
@@ -19497,7 +19997,7 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Jordan</t>
+          <t>JO</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
@@ -19667,6 +20167,11 @@
         </is>
       </c>
       <c r="AT101" t="inlineStr">
+        <is>
+          <t>Gizlan</t>
+        </is>
+      </c>
+      <c r="AU101" t="inlineStr">
         <is>
           <t>SKU-CF0DC20A55BA</t>
         </is>
@@ -19683,7 +20188,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AB12"/>
+  <dimension ref="A1:AC12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -19729,100 +20234,105 @@
       </c>
       <c r="I1" t="inlineStr">
         <is>
+          <t>Manufacturer Name</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
           <t>Seller SKU</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>price</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>Level 1*</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>Level 2*</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
+      <c r="N1" t="inlineStr">
         <is>
           <t>Level 3*</t>
         </is>
       </c>
-      <c r="N1" t="inlineStr">
+      <c r="O1" t="inlineStr">
         <is>
           <t>Risk Class *</t>
         </is>
       </c>
-      <c r="O1" t="inlineStr">
+      <c r="P1" t="inlineStr">
         <is>
           <t>Sterility</t>
         </is>
       </c>
-      <c r="P1" t="inlineStr">
+      <c r="Q1" t="inlineStr">
         <is>
           <t>Brand</t>
         </is>
       </c>
-      <c r="Q1" t="inlineStr">
+      <c r="R1" t="inlineStr">
         <is>
           <t>Model / Catalogue Number</t>
         </is>
       </c>
-      <c r="R1" t="inlineStr">
+      <c r="S1" t="inlineStr">
         <is>
           <t>Single Use</t>
         </is>
       </c>
-      <c r="S1" t="inlineStr">
+      <c r="T1" t="inlineStr">
         <is>
           <t>Legal Manufacturer</t>
         </is>
       </c>
-      <c r="T1" t="inlineStr">
+      <c r="U1" t="inlineStr">
         <is>
           <t>UDI-DI</t>
         </is>
       </c>
-      <c r="U1" t="inlineStr">
+      <c r="V1" t="inlineStr">
         <is>
           <t>GMDN Code / Term</t>
         </is>
       </c>
-      <c r="V1" t="inlineStr">
+      <c r="W1" t="inlineStr">
         <is>
           <t>SFDA Authorized Representative License No.</t>
         </is>
       </c>
-      <c r="W1" t="inlineStr">
+      <c r="X1" t="inlineStr">
         <is>
           <t>Size</t>
         </is>
       </c>
-      <c r="X1" t="inlineStr">
+      <c r="Y1" t="inlineStr">
         <is>
           <t>Power Source</t>
         </is>
       </c>
-      <c r="Y1" t="inlineStr">
+      <c r="Z1" t="inlineStr">
         <is>
           <t>Warranty</t>
         </is>
       </c>
-      <c r="Z1" t="inlineStr">
+      <c r="AA1" t="inlineStr">
         <is>
           <t>Storage Conditions / En</t>
         </is>
       </c>
-      <c r="AA1" t="inlineStr">
+      <c r="AB1" t="inlineStr">
         <is>
           <t>Usage Instructions</t>
         </is>
       </c>
-      <c r="AB1" t="inlineStr">
+      <c r="AC1" t="inlineStr">
         <is>
           <t>Branch id</t>
         </is>
@@ -19854,7 +20364,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -19869,92 +20379,97 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
+          <t>Yusur Medical</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
           <t>SKU-11484</t>
         </is>
       </c>
-      <c r="J2" t="n">
+      <c r="K2" t="n">
         <v>278.21</v>
       </c>
-      <c r="K2" t="inlineStr">
+      <c r="L2" t="inlineStr">
         <is>
           <t>Medical Devices &amp; Home Care</t>
         </is>
       </c>
-      <c r="L2" t="inlineStr">
+      <c r="M2" t="inlineStr">
         <is>
           <t>Home Care</t>
         </is>
       </c>
-      <c r="M2" t="inlineStr">
+      <c r="N2" t="inlineStr">
         <is>
           <t>Face Masks</t>
         </is>
       </c>
-      <c r="N2" t="inlineStr">
+      <c r="O2" t="inlineStr">
         <is>
           <t>Class I</t>
         </is>
       </c>
-      <c r="O2" t="inlineStr">
+      <c r="P2" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="P2" t="inlineStr">
+      <c r="Q2" t="inlineStr">
         <is>
           <t>Yusur Brand</t>
         </is>
       </c>
-      <c r="Q2" t="inlineStr">
+      <c r="R2" t="inlineStr">
         <is>
           <t>MD-100</t>
         </is>
       </c>
-      <c r="R2" t="inlineStr">
+      <c r="S2" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="S2" t="inlineStr">
+      <c r="T2" t="inlineStr">
         <is>
           <t>Yusur Medical</t>
         </is>
       </c>
-      <c r="T2" t="n">
-        <v>12345678905</v>
-      </c>
-      <c r="U2" t="inlineStr">
+      <c r="U2" t="n">
+        <v>430</v>
+      </c>
+      <c r="V2" t="inlineStr">
         <is>
           <t>12345/Term</t>
         </is>
       </c>
-      <c r="V2" t="inlineStr">
+      <c r="W2" t="inlineStr">
         <is>
           <t>SFDA123456</t>
         </is>
       </c>
-      <c r="W2" t="n">
+      <c r="X2" t="n">
         <v>100</v>
       </c>
-      <c r="X2" t="inlineStr">
+      <c r="Y2" t="inlineStr">
         <is>
           <t>Battery</t>
         </is>
       </c>
-      <c r="Y2" t="n">
+      <c r="Z2" t="n">
         <v>12</v>
       </c>
-      <c r="Z2" t="inlineStr">
+      <c r="AA2" t="inlineStr">
         <is>
           <t>Store below 25C</t>
         </is>
       </c>
-      <c r="AA2" t="inlineStr">
+      <c r="AB2" t="inlineStr">
         <is>
           <t>https://example.com/instructions.pdf</t>
         </is>
       </c>
-      <c r="AB2" t="inlineStr">
+      <c r="AC2" t="inlineStr">
         <is>
           <t>1,2,3</t>
         </is>
@@ -19986,7 +20501,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -20001,92 +20516,97 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
+          <t>Yusur Medical</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
           <t>SKU-54075</t>
         </is>
       </c>
-      <c r="J3" t="n">
+      <c r="K3" t="n">
         <v>68.65000000000001</v>
       </c>
-      <c r="K3" t="inlineStr">
+      <c r="L3" t="inlineStr">
         <is>
           <t>Medical Devices &amp; Home Care</t>
         </is>
       </c>
-      <c r="L3" t="inlineStr">
+      <c r="M3" t="inlineStr">
         <is>
           <t>Home Care</t>
         </is>
       </c>
-      <c r="M3" t="inlineStr">
+      <c r="N3" t="inlineStr">
         <is>
           <t>Face Masks</t>
         </is>
       </c>
-      <c r="N3" t="inlineStr">
+      <c r="O3" t="inlineStr">
         <is>
           <t>Class I</t>
         </is>
       </c>
-      <c r="O3" t="inlineStr">
+      <c r="P3" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="P3" t="inlineStr">
+      <c r="Q3" t="inlineStr">
         <is>
           <t>Yusur Brand</t>
         </is>
       </c>
-      <c r="Q3" t="inlineStr">
+      <c r="R3" t="inlineStr">
         <is>
           <t>MD-100</t>
         </is>
       </c>
-      <c r="R3" t="inlineStr">
+      <c r="S3" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="S3" t="inlineStr">
+      <c r="T3" t="inlineStr">
         <is>
           <t>Yusur Medical</t>
         </is>
       </c>
-      <c r="T3" t="n">
-        <v>12345678905</v>
-      </c>
-      <c r="U3" t="inlineStr">
+      <c r="U3" t="n">
+        <v>431</v>
+      </c>
+      <c r="V3" t="inlineStr">
         <is>
           <t>12345/Term</t>
         </is>
       </c>
-      <c r="V3" t="inlineStr">
+      <c r="W3" t="inlineStr">
         <is>
           <t>SFDA123456</t>
         </is>
       </c>
-      <c r="W3" t="n">
+      <c r="X3" t="n">
         <v>100</v>
       </c>
-      <c r="X3" t="inlineStr">
+      <c r="Y3" t="inlineStr">
         <is>
           <t>Battery</t>
         </is>
       </c>
-      <c r="Y3" t="n">
+      <c r="Z3" t="n">
         <v>12</v>
       </c>
-      <c r="Z3" t="inlineStr">
+      <c r="AA3" t="inlineStr">
         <is>
           <t>Store below 25C</t>
         </is>
       </c>
-      <c r="AA3" t="inlineStr">
+      <c r="AB3" t="inlineStr">
         <is>
           <t>https://example.com/instructions.pdf</t>
         </is>
       </c>
-      <c r="AB3" t="inlineStr">
+      <c r="AC3" t="inlineStr">
         <is>
           <t>1,2,3</t>
         </is>
@@ -20118,7 +20638,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -20133,92 +20653,97 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
+          <t>Yusur Medical</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
           <t>SKU-51446</t>
         </is>
       </c>
-      <c r="J4" t="n">
+      <c r="K4" t="n">
         <v>406.04</v>
       </c>
-      <c r="K4" t="inlineStr">
+      <c r="L4" t="inlineStr">
         <is>
           <t>Medical Devices &amp; Home Care</t>
         </is>
       </c>
-      <c r="L4" t="inlineStr">
+      <c r="M4" t="inlineStr">
         <is>
           <t>Home Care</t>
         </is>
       </c>
-      <c r="M4" t="inlineStr">
+      <c r="N4" t="inlineStr">
         <is>
           <t>Face Masks</t>
         </is>
       </c>
-      <c r="N4" t="inlineStr">
+      <c r="O4" t="inlineStr">
         <is>
           <t>Class I</t>
         </is>
       </c>
-      <c r="O4" t="inlineStr">
+      <c r="P4" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="P4" t="inlineStr">
+      <c r="Q4" t="inlineStr">
         <is>
           <t>Yusur Brand</t>
         </is>
       </c>
-      <c r="Q4" t="inlineStr">
+      <c r="R4" t="inlineStr">
         <is>
           <t>MD-100</t>
         </is>
       </c>
-      <c r="R4" t="inlineStr">
+      <c r="S4" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="S4" t="inlineStr">
+      <c r="T4" t="inlineStr">
         <is>
           <t>Yusur Medical</t>
         </is>
       </c>
-      <c r="T4" t="n">
-        <v>12345678905</v>
-      </c>
-      <c r="U4" t="inlineStr">
+      <c r="U4" t="n">
+        <v>432</v>
+      </c>
+      <c r="V4" t="inlineStr">
         <is>
           <t>12345/Term</t>
         </is>
       </c>
-      <c r="V4" t="inlineStr">
+      <c r="W4" t="inlineStr">
         <is>
           <t>SFDA123456</t>
         </is>
       </c>
-      <c r="W4" t="n">
+      <c r="X4" t="n">
         <v>100</v>
       </c>
-      <c r="X4" t="inlineStr">
+      <c r="Y4" t="inlineStr">
         <is>
           <t>Battery</t>
         </is>
       </c>
-      <c r="Y4" t="n">
+      <c r="Z4" t="n">
         <v>12</v>
       </c>
-      <c r="Z4" t="inlineStr">
+      <c r="AA4" t="inlineStr">
         <is>
           <t>Store below 25C</t>
         </is>
       </c>
-      <c r="AA4" t="inlineStr">
+      <c r="AB4" t="inlineStr">
         <is>
           <t>https://example.com/instructions.pdf</t>
         </is>
       </c>
-      <c r="AB4" t="inlineStr">
+      <c r="AC4" t="inlineStr">
         <is>
           <t>1,2,3</t>
         </is>
@@ -20250,7 +20775,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -20265,92 +20790,97 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
+          <t>Yusur Medical</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
           <t>SKU-83989</t>
         </is>
       </c>
-      <c r="J5" t="n">
+      <c r="K5" t="n">
         <v>206.87</v>
       </c>
-      <c r="K5" t="inlineStr">
+      <c r="L5" t="inlineStr">
         <is>
           <t>Medical Devices &amp; Home Care</t>
         </is>
       </c>
-      <c r="L5" t="inlineStr">
+      <c r="M5" t="inlineStr">
         <is>
           <t>Home Care</t>
         </is>
       </c>
-      <c r="M5" t="inlineStr">
+      <c r="N5" t="inlineStr">
         <is>
           <t>Face Masks</t>
         </is>
       </c>
-      <c r="N5" t="inlineStr">
+      <c r="O5" t="inlineStr">
         <is>
           <t>Class I</t>
         </is>
       </c>
-      <c r="O5" t="inlineStr">
+      <c r="P5" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="P5" t="inlineStr">
+      <c r="Q5" t="inlineStr">
         <is>
           <t>Yusur Brand</t>
         </is>
       </c>
-      <c r="Q5" t="inlineStr">
+      <c r="R5" t="inlineStr">
         <is>
           <t>MD-100</t>
         </is>
       </c>
-      <c r="R5" t="inlineStr">
+      <c r="S5" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="S5" t="inlineStr">
+      <c r="T5" t="inlineStr">
         <is>
           <t>Yusur Medical</t>
         </is>
       </c>
-      <c r="T5" t="n">
-        <v>12345678905</v>
-      </c>
-      <c r="U5" t="inlineStr">
+      <c r="U5" t="n">
+        <v>433</v>
+      </c>
+      <c r="V5" t="inlineStr">
         <is>
           <t>12345/Term</t>
         </is>
       </c>
-      <c r="V5" t="inlineStr">
+      <c r="W5" t="inlineStr">
         <is>
           <t>SFDA123456</t>
         </is>
       </c>
-      <c r="W5" t="n">
+      <c r="X5" t="n">
         <v>100</v>
       </c>
-      <c r="X5" t="inlineStr">
+      <c r="Y5" t="inlineStr">
         <is>
           <t>Battery</t>
         </is>
       </c>
-      <c r="Y5" t="n">
+      <c r="Z5" t="n">
         <v>12</v>
       </c>
-      <c r="Z5" t="inlineStr">
+      <c r="AA5" t="inlineStr">
         <is>
           <t>Store below 25C</t>
         </is>
       </c>
-      <c r="AA5" t="inlineStr">
+      <c r="AB5" t="inlineStr">
         <is>
           <t>https://example.com/instructions.pdf</t>
         </is>
       </c>
-      <c r="AB5" t="inlineStr">
+      <c r="AC5" t="inlineStr">
         <is>
           <t>1,2,3</t>
         </is>
@@ -20382,7 +20912,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -20397,92 +20927,97 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
+          <t>Yusur Medical</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
           <t>SKU-48723</t>
         </is>
       </c>
-      <c r="J6" t="n">
+      <c r="K6" t="n">
         <v>353.61</v>
       </c>
-      <c r="K6" t="inlineStr">
+      <c r="L6" t="inlineStr">
         <is>
           <t>Medical Devices &amp; Home Care</t>
         </is>
       </c>
-      <c r="L6" t="inlineStr">
+      <c r="M6" t="inlineStr">
         <is>
           <t>Home Care</t>
         </is>
       </c>
-      <c r="M6" t="inlineStr">
+      <c r="N6" t="inlineStr">
         <is>
           <t>Face Masks</t>
         </is>
       </c>
-      <c r="N6" t="inlineStr">
+      <c r="O6" t="inlineStr">
         <is>
           <t>Class I</t>
         </is>
       </c>
-      <c r="O6" t="inlineStr">
+      <c r="P6" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="P6" t="inlineStr">
+      <c r="Q6" t="inlineStr">
         <is>
           <t>Yusur Brand</t>
         </is>
       </c>
-      <c r="Q6" t="inlineStr">
+      <c r="R6" t="inlineStr">
         <is>
           <t>MD-100</t>
         </is>
       </c>
-      <c r="R6" t="inlineStr">
+      <c r="S6" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="S6" t="inlineStr">
+      <c r="T6" t="inlineStr">
         <is>
           <t>Yusur Medical</t>
         </is>
       </c>
-      <c r="T6" t="n">
-        <v>12345678905</v>
-      </c>
-      <c r="U6" t="inlineStr">
+      <c r="U6" t="n">
+        <v>434</v>
+      </c>
+      <c r="V6" t="inlineStr">
         <is>
           <t>12345/Term</t>
         </is>
       </c>
-      <c r="V6" t="inlineStr">
+      <c r="W6" t="inlineStr">
         <is>
           <t>SFDA123456</t>
         </is>
       </c>
-      <c r="W6" t="n">
+      <c r="X6" t="n">
         <v>100</v>
       </c>
-      <c r="X6" t="inlineStr">
+      <c r="Y6" t="inlineStr">
         <is>
           <t>Battery</t>
         </is>
       </c>
-      <c r="Y6" t="n">
+      <c r="Z6" t="n">
         <v>12</v>
       </c>
-      <c r="Z6" t="inlineStr">
+      <c r="AA6" t="inlineStr">
         <is>
           <t>Store below 25C</t>
         </is>
       </c>
-      <c r="AA6" t="inlineStr">
+      <c r="AB6" t="inlineStr">
         <is>
           <t>https://example.com/instructions.pdf</t>
         </is>
       </c>
-      <c r="AB6" t="inlineStr">
+      <c r="AC6" t="inlineStr">
         <is>
           <t>1,2,3</t>
         </is>
@@ -20514,7 +21049,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -20529,92 +21064,97 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
+          <t>Yusur Medical</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
           <t>SKU-21826</t>
         </is>
       </c>
-      <c r="J7" t="n">
+      <c r="K7" t="n">
         <v>443.18</v>
       </c>
-      <c r="K7" t="inlineStr">
+      <c r="L7" t="inlineStr">
         <is>
           <t>Medical Devices &amp; Home Care</t>
         </is>
       </c>
-      <c r="L7" t="inlineStr">
+      <c r="M7" t="inlineStr">
         <is>
           <t>Home Care</t>
         </is>
       </c>
-      <c r="M7" t="inlineStr">
+      <c r="N7" t="inlineStr">
         <is>
           <t>Face Masks</t>
         </is>
       </c>
-      <c r="N7" t="inlineStr">
+      <c r="O7" t="inlineStr">
         <is>
           <t>Class I</t>
         </is>
       </c>
-      <c r="O7" t="inlineStr">
+      <c r="P7" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="P7" t="inlineStr">
+      <c r="Q7" t="inlineStr">
         <is>
           <t>Yusur Brand</t>
         </is>
       </c>
-      <c r="Q7" t="inlineStr">
+      <c r="R7" t="inlineStr">
         <is>
           <t>MD-100</t>
         </is>
       </c>
-      <c r="R7" t="inlineStr">
+      <c r="S7" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="S7" t="inlineStr">
+      <c r="T7" t="inlineStr">
         <is>
           <t>Yusur Medical</t>
         </is>
       </c>
-      <c r="T7" t="n">
-        <v>12345678905</v>
-      </c>
-      <c r="U7" t="inlineStr">
+      <c r="U7" t="n">
+        <v>435</v>
+      </c>
+      <c r="V7" t="inlineStr">
         <is>
           <t>12345/Term</t>
         </is>
       </c>
-      <c r="V7" t="inlineStr">
+      <c r="W7" t="inlineStr">
         <is>
           <t>SFDA123456</t>
         </is>
       </c>
-      <c r="W7" t="n">
+      <c r="X7" t="n">
         <v>100</v>
       </c>
-      <c r="X7" t="inlineStr">
+      <c r="Y7" t="inlineStr">
         <is>
           <t>Battery</t>
         </is>
       </c>
-      <c r="Y7" t="n">
+      <c r="Z7" t="n">
         <v>12</v>
       </c>
-      <c r="Z7" t="inlineStr">
+      <c r="AA7" t="inlineStr">
         <is>
           <t>Store below 25C</t>
         </is>
       </c>
-      <c r="AA7" t="inlineStr">
+      <c r="AB7" t="inlineStr">
         <is>
           <t>https://example.com/instructions.pdf</t>
         </is>
       </c>
-      <c r="AB7" t="inlineStr">
+      <c r="AC7" t="inlineStr">
         <is>
           <t>1,2,3</t>
         </is>
@@ -20646,7 +21186,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -20661,92 +21201,97 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
+          <t>Yusur Medical</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
           <t>SKU-91350</t>
         </is>
       </c>
-      <c r="J8" t="n">
+      <c r="K8" t="n">
         <v>224.49</v>
       </c>
-      <c r="K8" t="inlineStr">
+      <c r="L8" t="inlineStr">
         <is>
           <t>Medical Devices &amp; Home Care</t>
         </is>
       </c>
-      <c r="L8" t="inlineStr">
+      <c r="M8" t="inlineStr">
         <is>
           <t>Home Care</t>
         </is>
       </c>
-      <c r="M8" t="inlineStr">
+      <c r="N8" t="inlineStr">
         <is>
           <t>Face Masks</t>
         </is>
       </c>
-      <c r="N8" t="inlineStr">
+      <c r="O8" t="inlineStr">
         <is>
           <t>Class I</t>
         </is>
       </c>
-      <c r="O8" t="inlineStr">
+      <c r="P8" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="P8" t="inlineStr">
+      <c r="Q8" t="inlineStr">
         <is>
           <t>Yusur Brand</t>
         </is>
       </c>
-      <c r="Q8" t="inlineStr">
+      <c r="R8" t="inlineStr">
         <is>
           <t>MD-100</t>
         </is>
       </c>
-      <c r="R8" t="inlineStr">
+      <c r="S8" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="S8" t="inlineStr">
+      <c r="T8" t="inlineStr">
         <is>
           <t>Yusur Medical</t>
         </is>
       </c>
-      <c r="T8" t="n">
-        <v>12345678905</v>
-      </c>
-      <c r="U8" t="inlineStr">
+      <c r="U8" t="n">
+        <v>436</v>
+      </c>
+      <c r="V8" t="inlineStr">
         <is>
           <t>12345/Term</t>
         </is>
       </c>
-      <c r="V8" t="inlineStr">
+      <c r="W8" t="inlineStr">
         <is>
           <t>SFDA123456</t>
         </is>
       </c>
-      <c r="W8" t="n">
+      <c r="X8" t="n">
         <v>100</v>
       </c>
-      <c r="X8" t="inlineStr">
+      <c r="Y8" t="inlineStr">
         <is>
           <t>Battery</t>
         </is>
       </c>
-      <c r="Y8" t="n">
+      <c r="Z8" t="n">
         <v>12</v>
       </c>
-      <c r="Z8" t="inlineStr">
+      <c r="AA8" t="inlineStr">
         <is>
           <t>Store below 25C</t>
         </is>
       </c>
-      <c r="AA8" t="inlineStr">
+      <c r="AB8" t="inlineStr">
         <is>
           <t>https://example.com/instructions.pdf</t>
         </is>
       </c>
-      <c r="AB8" t="inlineStr">
+      <c r="AC8" t="inlineStr">
         <is>
           <t>1,2,3</t>
         </is>
@@ -20778,7 +21323,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -20793,92 +21338,97 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
+          <t>Yusur Medical</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
           <t>SKU-10868</t>
         </is>
       </c>
-      <c r="J9" t="n">
+      <c r="K9" t="n">
         <v>301.48</v>
       </c>
-      <c r="K9" t="inlineStr">
+      <c r="L9" t="inlineStr">
         <is>
           <t>Medical Devices &amp; Home Care</t>
         </is>
       </c>
-      <c r="L9" t="inlineStr">
+      <c r="M9" t="inlineStr">
         <is>
           <t>Home Care</t>
         </is>
       </c>
-      <c r="M9" t="inlineStr">
+      <c r="N9" t="inlineStr">
         <is>
           <t>Face Masks</t>
         </is>
       </c>
-      <c r="N9" t="inlineStr">
+      <c r="O9" t="inlineStr">
         <is>
           <t>Class I</t>
         </is>
       </c>
-      <c r="O9" t="inlineStr">
+      <c r="P9" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="P9" t="inlineStr">
+      <c r="Q9" t="inlineStr">
         <is>
           <t>Yusur Brand</t>
         </is>
       </c>
-      <c r="Q9" t="inlineStr">
+      <c r="R9" t="inlineStr">
         <is>
           <t>MD-100</t>
         </is>
       </c>
-      <c r="R9" t="inlineStr">
+      <c r="S9" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="S9" t="inlineStr">
+      <c r="T9" t="inlineStr">
         <is>
           <t>Yusur Medical</t>
         </is>
       </c>
-      <c r="T9" t="n">
-        <v>12345678905</v>
-      </c>
-      <c r="U9" t="inlineStr">
+      <c r="U9" t="n">
+        <v>437</v>
+      </c>
+      <c r="V9" t="inlineStr">
         <is>
           <t>12345/Term</t>
         </is>
       </c>
-      <c r="V9" t="inlineStr">
+      <c r="W9" t="inlineStr">
         <is>
           <t>SFDA123456</t>
         </is>
       </c>
-      <c r="W9" t="n">
+      <c r="X9" t="n">
         <v>100</v>
       </c>
-      <c r="X9" t="inlineStr">
+      <c r="Y9" t="inlineStr">
         <is>
           <t>Battery</t>
         </is>
       </c>
-      <c r="Y9" t="n">
+      <c r="Z9" t="n">
         <v>12</v>
       </c>
-      <c r="Z9" t="inlineStr">
+      <c r="AA9" t="inlineStr">
         <is>
           <t>Store below 25C</t>
         </is>
       </c>
-      <c r="AA9" t="inlineStr">
+      <c r="AB9" t="inlineStr">
         <is>
           <t>https://example.com/instructions.pdf</t>
         </is>
       </c>
-      <c r="AB9" t="inlineStr">
+      <c r="AC9" t="inlineStr">
         <is>
           <t>1,2,3</t>
         </is>
@@ -20910,7 +21460,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -20925,92 +21475,97 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
+          <t>Yusur Medical</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
           <t>SKU-12512</t>
         </is>
       </c>
-      <c r="J10" t="n">
+      <c r="K10" t="n">
         <v>289.34</v>
       </c>
-      <c r="K10" t="inlineStr">
+      <c r="L10" t="inlineStr">
         <is>
           <t>Medical Devices &amp; Home Care</t>
         </is>
       </c>
-      <c r="L10" t="inlineStr">
+      <c r="M10" t="inlineStr">
         <is>
           <t>Home Care</t>
         </is>
       </c>
-      <c r="M10" t="inlineStr">
+      <c r="N10" t="inlineStr">
         <is>
           <t>Face Masks</t>
         </is>
       </c>
-      <c r="N10" t="inlineStr">
+      <c r="O10" t="inlineStr">
         <is>
           <t>Class I</t>
         </is>
       </c>
-      <c r="O10" t="inlineStr">
+      <c r="P10" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="P10" t="inlineStr">
+      <c r="Q10" t="inlineStr">
         <is>
           <t>Yusur Brand</t>
         </is>
       </c>
-      <c r="Q10" t="inlineStr">
+      <c r="R10" t="inlineStr">
         <is>
           <t>MD-100</t>
         </is>
       </c>
-      <c r="R10" t="inlineStr">
+      <c r="S10" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="S10" t="inlineStr">
+      <c r="T10" t="inlineStr">
         <is>
           <t>Yusur Medical</t>
         </is>
       </c>
-      <c r="T10" t="n">
-        <v>12345678905</v>
-      </c>
-      <c r="U10" t="inlineStr">
+      <c r="U10" t="n">
+        <v>438</v>
+      </c>
+      <c r="V10" t="inlineStr">
         <is>
           <t>12345/Term</t>
         </is>
       </c>
-      <c r="V10" t="inlineStr">
+      <c r="W10" t="inlineStr">
         <is>
           <t>SFDA123456</t>
         </is>
       </c>
-      <c r="W10" t="n">
+      <c r="X10" t="n">
         <v>100</v>
       </c>
-      <c r="X10" t="inlineStr">
+      <c r="Y10" t="inlineStr">
         <is>
           <t>Battery</t>
         </is>
       </c>
-      <c r="Y10" t="n">
+      <c r="Z10" t="n">
         <v>12</v>
       </c>
-      <c r="Z10" t="inlineStr">
+      <c r="AA10" t="inlineStr">
         <is>
           <t>Store below 25C</t>
         </is>
       </c>
-      <c r="AA10" t="inlineStr">
+      <c r="AB10" t="inlineStr">
         <is>
           <t>https://example.com/instructions.pdf</t>
         </is>
       </c>
-      <c r="AB10" t="inlineStr">
+      <c r="AC10" t="inlineStr">
         <is>
           <t>1,2,3</t>
         </is>
@@ -21042,7 +21597,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -21057,92 +21612,97 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
+          <t>Yusur Medical</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
           <t>SKU-65491</t>
         </is>
       </c>
-      <c r="J11" t="n">
+      <c r="K11" t="n">
         <v>151.72</v>
       </c>
-      <c r="K11" t="inlineStr">
+      <c r="L11" t="inlineStr">
         <is>
           <t>Medical Devices &amp; Home Care</t>
         </is>
       </c>
-      <c r="L11" t="inlineStr">
+      <c r="M11" t="inlineStr">
         <is>
           <t>Home Care</t>
         </is>
       </c>
-      <c r="M11" t="inlineStr">
+      <c r="N11" t="inlineStr">
         <is>
           <t>Face Masks</t>
         </is>
       </c>
-      <c r="N11" t="inlineStr">
+      <c r="O11" t="inlineStr">
         <is>
           <t>Class I</t>
         </is>
       </c>
-      <c r="O11" t="inlineStr">
+      <c r="P11" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="P11" t="inlineStr">
+      <c r="Q11" t="inlineStr">
         <is>
           <t>Yusur Brand</t>
         </is>
       </c>
-      <c r="Q11" t="inlineStr">
+      <c r="R11" t="inlineStr">
         <is>
           <t>MD-100</t>
         </is>
       </c>
-      <c r="R11" t="inlineStr">
+      <c r="S11" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="S11" t="inlineStr">
+      <c r="T11" t="inlineStr">
         <is>
           <t>Yusur Medical</t>
         </is>
       </c>
-      <c r="T11" t="n">
-        <v>12345678905</v>
-      </c>
-      <c r="U11" t="inlineStr">
+      <c r="U11" t="n">
+        <v>439</v>
+      </c>
+      <c r="V11" t="inlineStr">
         <is>
           <t>12345/Term</t>
         </is>
       </c>
-      <c r="V11" t="inlineStr">
+      <c r="W11" t="inlineStr">
         <is>
           <t>SFDA123456</t>
         </is>
       </c>
-      <c r="W11" t="n">
+      <c r="X11" t="n">
         <v>100</v>
       </c>
-      <c r="X11" t="inlineStr">
+      <c r="Y11" t="inlineStr">
         <is>
           <t>Battery</t>
         </is>
       </c>
-      <c r="Y11" t="n">
+      <c r="Z11" t="n">
         <v>12</v>
       </c>
-      <c r="Z11" t="inlineStr">
+      <c r="AA11" t="inlineStr">
         <is>
           <t>Store below 25C</t>
         </is>
       </c>
-      <c r="AA11" t="inlineStr">
+      <c r="AB11" t="inlineStr">
         <is>
           <t>https://example.com/instructions.pdf</t>
         </is>
       </c>
-      <c r="AB11" t="inlineStr">
+      <c r="AC11" t="inlineStr">
         <is>
           <t>1,2,3</t>
         </is>
@@ -21174,7 +21734,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -21189,92 +21749,97 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
+          <t>Yusur Medical</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
           <t>SKU-81972</t>
         </is>
       </c>
-      <c r="J12" t="n">
+      <c r="K12" t="n">
         <v>246.38</v>
       </c>
-      <c r="K12" t="inlineStr">
+      <c r="L12" t="inlineStr">
         <is>
           <t>Medical Devices &amp; Home Care</t>
         </is>
       </c>
-      <c r="L12" t="inlineStr">
+      <c r="M12" t="inlineStr">
         <is>
           <t>Home Care</t>
         </is>
       </c>
-      <c r="M12" t="inlineStr">
+      <c r="N12" t="inlineStr">
         <is>
           <t>Face Masks</t>
         </is>
       </c>
-      <c r="N12" t="inlineStr">
+      <c r="O12" t="inlineStr">
         <is>
           <t>Class I</t>
         </is>
       </c>
-      <c r="O12" t="inlineStr">
+      <c r="P12" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="P12" t="inlineStr">
+      <c r="Q12" t="inlineStr">
         <is>
           <t>Yusur Brand</t>
         </is>
       </c>
-      <c r="Q12" t="inlineStr">
+      <c r="R12" t="inlineStr">
         <is>
           <t>MD-100</t>
         </is>
       </c>
-      <c r="R12" t="inlineStr">
+      <c r="S12" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="S12" t="inlineStr">
+      <c r="T12" t="inlineStr">
         <is>
           <t>Yusur Medical</t>
         </is>
       </c>
-      <c r="T12" t="n">
-        <v>12345678905</v>
-      </c>
-      <c r="U12" t="inlineStr">
+      <c r="U12" t="n">
+        <v>440</v>
+      </c>
+      <c r="V12" t="inlineStr">
         <is>
           <t>12345/Term</t>
         </is>
       </c>
-      <c r="V12" t="inlineStr">
+      <c r="W12" t="inlineStr">
         <is>
           <t>SFDA123456</t>
         </is>
       </c>
-      <c r="W12" t="n">
+      <c r="X12" t="n">
         <v>100</v>
       </c>
-      <c r="X12" t="inlineStr">
+      <c r="Y12" t="inlineStr">
         <is>
           <t>Battery</t>
         </is>
       </c>
-      <c r="Y12" t="n">
+      <c r="Z12" t="n">
         <v>12</v>
       </c>
-      <c r="Z12" t="inlineStr">
+      <c r="AA12" t="inlineStr">
         <is>
           <t>Store below 25C</t>
         </is>
       </c>
-      <c r="AA12" t="inlineStr">
+      <c r="AB12" t="inlineStr">
         <is>
           <t>https://example.com/instructions.pdf</t>
         </is>
       </c>
-      <c r="AB12" t="inlineStr">
+      <c r="AC12" t="inlineStr">
         <is>
           <t>1,2,3</t>
         </is>
@@ -21291,7 +21856,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U21"/>
+  <dimension ref="A1:W21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -21397,6 +21962,16 @@
       </c>
       <c r="U1" t="inlineStr">
         <is>
+          <t>Manufacturer Name</t>
+        </is>
+      </c>
+      <c r="V1" t="inlineStr">
+        <is>
+          <t>Ingredients</t>
+        </is>
+      </c>
+      <c r="W1" t="inlineStr">
+        <is>
           <t>Seller SKU</t>
         </is>
       </c>
@@ -21432,7 +22007,7 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -21497,6 +22072,16 @@
         </is>
       </c>
       <c r="U2" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V2" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W2" t="inlineStr">
         <is>
           <t>SKU-4D84A7801DF2</t>
         </is>
@@ -21533,7 +22118,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -21598,6 +22183,16 @@
         </is>
       </c>
       <c r="U3" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
         <is>
           <t>SKU-7D3981EB4DFD</t>
         </is>
@@ -21634,7 +22229,7 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -21699,6 +22294,16 @@
         </is>
       </c>
       <c r="U4" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
         <is>
           <t>SKU-ED3AD3119B91</t>
         </is>
@@ -21735,7 +22340,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -21800,6 +22405,16 @@
         </is>
       </c>
       <c r="U5" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
         <is>
           <t>SKU-02643680E63F</t>
         </is>
@@ -21836,7 +22451,7 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -21901,6 +22516,16 @@
         </is>
       </c>
       <c r="U6" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
         <is>
           <t>SKU-0F0ECCC0A873</t>
         </is>
@@ -21937,7 +22562,7 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -22002,6 +22627,16 @@
         </is>
       </c>
       <c r="U7" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
         <is>
           <t>SKU-CAEEDF73C949</t>
         </is>
@@ -22038,7 +22673,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -22103,6 +22738,16 @@
         </is>
       </c>
       <c r="U8" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
         <is>
           <t>SKU-68F2D92F6DD1</t>
         </is>
@@ -22139,7 +22784,7 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -22204,6 +22849,16 @@
         </is>
       </c>
       <c r="U9" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
         <is>
           <t>SKU-02BBE68D4F6D</t>
         </is>
@@ -22240,7 +22895,7 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -22305,6 +22960,16 @@
         </is>
       </c>
       <c r="U10" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
         <is>
           <t>SKU-A68FB608CF37</t>
         </is>
@@ -22341,7 +23006,7 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -22406,6 +23071,16 @@
         </is>
       </c>
       <c r="U11" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
         <is>
           <t>SKU-7DB0D2EDB3AF</t>
         </is>
@@ -22442,7 +23117,7 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -22507,6 +23182,16 @@
         </is>
       </c>
       <c r="U12" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
         <is>
           <t>SKU-FB44592CEA6F</t>
         </is>
@@ -22543,7 +23228,7 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -22608,6 +23293,16 @@
         </is>
       </c>
       <c r="U13" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
         <is>
           <t>SKU-4FC2715666EA</t>
         </is>
@@ -22644,7 +23339,7 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -22709,6 +23404,16 @@
         </is>
       </c>
       <c r="U14" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
         <is>
           <t>SKU-B3A3CDA5754A</t>
         </is>
@@ -22745,7 +23450,7 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -22810,6 +23515,16 @@
         </is>
       </c>
       <c r="U15" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
         <is>
           <t>SKU-05C2765669C5</t>
         </is>
@@ -22846,7 +23561,7 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -22911,6 +23626,16 @@
         </is>
       </c>
       <c r="U16" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
         <is>
           <t>SKU-48A97B5F9AA2</t>
         </is>
@@ -22947,7 +23672,7 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -23012,6 +23737,16 @@
         </is>
       </c>
       <c r="U17" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
         <is>
           <t>SKU-5280EA87DFF4</t>
         </is>
@@ -23048,7 +23783,7 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -23113,6 +23848,16 @@
         </is>
       </c>
       <c r="U18" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
         <is>
           <t>SKU-CB8062C2620C</t>
         </is>
@@ -23149,7 +23894,7 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -23214,6 +23959,16 @@
         </is>
       </c>
       <c r="U19" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
         <is>
           <t>SKU-DDA5F16D3EAF</t>
         </is>
@@ -23250,7 +24005,7 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -23315,6 +24070,16 @@
         </is>
       </c>
       <c r="U20" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
         <is>
           <t>SKU-09C077532E92</t>
         </is>
@@ -23351,7 +24116,7 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Saudi Arabia</t>
+          <t>SA</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
@@ -23416,6 +24181,16 @@
         </is>
       </c>
       <c r="U21" t="inlineStr">
+        <is>
+          <t>Yusur Pharma</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Aqua, Glycerin</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
         <is>
           <t>SKU-A75808CE4D3E</t>
         </is>

--- a/product_upload/packages/46/file.xlsx
+++ b/product_upload/packages/46/file.xlsx
@@ -686,8 +686,16 @@
           <t>4738237411-112-716941231256</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr"/>
-      <c r="H2" t="inlineStr"/>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ Ribex</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>Ribex detailed description.</t>
+        </is>
+      </c>
       <c r="I2" t="n">
         <v>0</v>
       </c>
@@ -869,8 +877,16 @@
           <t>6214599023-179-171280008525</t>
         </is>
       </c>
-      <c r="G3" t="inlineStr"/>
-      <c r="H3" t="inlineStr"/>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ CO-Ribex</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>CO-Ribex detailed description.</t>
+        </is>
+      </c>
       <c r="I3" t="n">
         <v>0</v>
       </c>
@@ -1056,8 +1072,16 @@
           <t>5820766162-513-698326912187</t>
         </is>
       </c>
-      <c r="G4" t="inlineStr"/>
-      <c r="H4" t="inlineStr"/>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ CO-Ribex</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>CO-Ribex detailed description.</t>
+        </is>
+      </c>
       <c r="I4" t="n">
         <v>0</v>
       </c>
@@ -1251,8 +1275,16 @@
           <t>1952998614-646-951517567597</t>
         </is>
       </c>
-      <c r="G5" t="inlineStr"/>
-      <c r="H5" t="inlineStr"/>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ CO-Ribex</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>CO-Ribex detailed description.</t>
+        </is>
+      </c>
       <c r="I5" t="n">
         <v>0</v>
       </c>
@@ -1637,8 +1669,16 @@
           <t>9297415498-701-749870053909</t>
         </is>
       </c>
-      <c r="G7" t="inlineStr"/>
-      <c r="H7" t="inlineStr"/>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ Resincalcio</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>Resincalcio detailed description.</t>
+        </is>
+      </c>
       <c r="I7" t="n">
         <v>0</v>
       </c>
@@ -2029,8 +2069,16 @@
           <t>7905093261-687-705141384227</t>
         </is>
       </c>
-      <c r="G9" t="inlineStr"/>
-      <c r="H9" t="inlineStr"/>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ Glevate</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>Glevate detailed description.</t>
+        </is>
+      </c>
       <c r="I9" t="n">
         <v>0</v>
       </c>
@@ -2415,8 +2463,16 @@
           <t>5794067026-042-622476354099</t>
         </is>
       </c>
-      <c r="G11" t="inlineStr"/>
-      <c r="H11" t="inlineStr"/>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ Basaglar Tempo Pen</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>Basaglar Tempo Pen detailed description.</t>
+        </is>
+      </c>
       <c r="I11" t="n">
         <v>0</v>
       </c>
@@ -2614,8 +2670,16 @@
           <t>1896327707-338-392565486975</t>
         </is>
       </c>
-      <c r="G12" t="inlineStr"/>
-      <c r="H12" t="inlineStr"/>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ Humalog Tempo Pen</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>Humalog Tempo Pen detailed description.</t>
+        </is>
+      </c>
       <c r="I12" t="n">
         <v>0</v>
       </c>
@@ -2805,8 +2869,16 @@
           <t>0960696938-536-096385098245</t>
         </is>
       </c>
-      <c r="G13" t="inlineStr"/>
-      <c r="H13" t="inlineStr"/>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ FANCATA 100MG TABLET</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>FANCATA 100MG TABLET detailed description.</t>
+        </is>
+      </c>
       <c r="I13" t="inlineStr">
         <is>
           <t>SPIMACO</t>
@@ -2994,8 +3066,16 @@
           <t>8238861185-137-294436497169</t>
         </is>
       </c>
-      <c r="G14" t="inlineStr"/>
-      <c r="H14" t="inlineStr"/>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ FANCATA 50MG TABLET</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>FANCATA 50MG TABLET detailed description.</t>
+        </is>
+      </c>
       <c r="I14" t="inlineStr">
         <is>
           <t>SPIMACO</t>
@@ -3191,8 +3271,16 @@
           <t>3779702233-074-869939088085</t>
         </is>
       </c>
-      <c r="G15" t="inlineStr"/>
-      <c r="H15" t="inlineStr"/>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ MOBIXEN</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>MOBIXEN detailed description.</t>
+        </is>
+      </c>
       <c r="I15" t="n">
         <v>0</v>
       </c>
@@ -3589,8 +3677,16 @@
           <t>1352655297-302-717742954848</t>
         </is>
       </c>
-      <c r="G17" t="inlineStr"/>
-      <c r="H17" t="inlineStr"/>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ NOXAFIL</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>NOXAFIL detailed description.</t>
+        </is>
+      </c>
       <c r="I17" t="n">
         <v>0</v>
       </c>
@@ -3780,8 +3876,16 @@
           <t>5824322406-670-180716329368</t>
         </is>
       </c>
-      <c r="G18" t="inlineStr"/>
-      <c r="H18" t="inlineStr"/>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ Irma-HCT 150 mg / 12.5 mg</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>Irma-HCT 150 mg / 12.5 mg detailed description.</t>
+        </is>
+      </c>
       <c r="I18" t="n">
         <v>0</v>
       </c>
@@ -3971,8 +4075,16 @@
           <t>6412151418-701-868534375991</t>
         </is>
       </c>
-      <c r="G19" t="inlineStr"/>
-      <c r="H19" t="inlineStr"/>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ IRMA-HCT 300 mg / 12.5 mg</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>IRMA-HCT 300 mg / 12.5 mg detailed description.</t>
+        </is>
+      </c>
       <c r="I19" t="n">
         <v>0</v>
       </c>
@@ -4166,8 +4278,16 @@
           <t>2802974060-618-366457728853</t>
         </is>
       </c>
-      <c r="G20" t="inlineStr"/>
-      <c r="H20" t="inlineStr"/>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ ADOL</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>ADOL detailed description.</t>
+        </is>
+      </c>
       <c r="I20" t="n">
         <v>0</v>
       </c>
@@ -4357,8 +4477,16 @@
           <t>4931978982-867-715954465368</t>
         </is>
       </c>
-      <c r="G21" t="inlineStr"/>
-      <c r="H21" t="inlineStr"/>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ ADOL</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>ADOL detailed description.</t>
+        </is>
+      </c>
       <c r="I21" t="n">
         <v>0</v>
       </c>
@@ -4544,8 +4672,16 @@
           <t>1560570476-816-258342097406</t>
         </is>
       </c>
-      <c r="G22" t="inlineStr"/>
-      <c r="H22" t="inlineStr"/>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ ADOL</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>ADOL detailed description.</t>
+        </is>
+      </c>
       <c r="I22" t="n">
         <v>0</v>
       </c>
@@ -4735,8 +4871,16 @@
           <t>0528353639-630-066961932588</t>
         </is>
       </c>
-      <c r="G23" t="inlineStr"/>
-      <c r="H23" t="inlineStr"/>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ VIDONORM 5MG/4MG TABLET</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>VIDONORM 5MG/4MG TABLET detailed description.</t>
+        </is>
+      </c>
       <c r="I23" t="inlineStr">
         <is>
           <t>AJA PHARMACEUTICAL INDUSTRIES</t>
@@ -4932,8 +5076,16 @@
           <t>0368520911-926-315249668250</t>
         </is>
       </c>
-      <c r="G24" t="inlineStr"/>
-      <c r="H24" t="inlineStr"/>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ VIDONORM 5MG/8MG TABLET</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>VIDONORM 5MG/8MG TABLET detailed description.</t>
+        </is>
+      </c>
       <c r="I24" t="inlineStr">
         <is>
           <t>AJA PHARMACEUTICAL INDUSTRIES</t>
@@ -5129,8 +5281,16 @@
           <t>2824445586-334-197636514193</t>
         </is>
       </c>
-      <c r="G25" t="inlineStr"/>
-      <c r="H25" t="inlineStr"/>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ VIDONORM 10MG/4MG TABLET</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>VIDONORM 10MG/4MG TABLET detailed description.</t>
+        </is>
+      </c>
       <c r="I25" t="inlineStr">
         <is>
           <t>AJA PHARMACEUTICAL INDUSTRIES</t>
@@ -5326,8 +5486,16 @@
           <t>7449283377-803-538609258777</t>
         </is>
       </c>
-      <c r="G26" t="inlineStr"/>
-      <c r="H26" t="inlineStr"/>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ VIDONORM 10MG/8MG TABLET</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>VIDONORM 10MG/8MG TABLET detailed description.</t>
+        </is>
+      </c>
       <c r="I26" t="inlineStr">
         <is>
           <t>AJA PHARMACEUTICAL INDUSTRIES</t>
@@ -6504,8 +6672,16 @@
           <t>6136362247-635-232486301445</t>
         </is>
       </c>
-      <c r="G32" t="inlineStr"/>
-      <c r="H32" t="inlineStr"/>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ Aryzalera</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>Aryzalera detailed description.</t>
+        </is>
+      </c>
       <c r="I32" t="n">
         <v>0</v>
       </c>
@@ -6691,8 +6867,16 @@
           <t>8745175260-020-069305113746</t>
         </is>
       </c>
-      <c r="G33" t="inlineStr"/>
-      <c r="H33" t="inlineStr"/>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ Aryzalera</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>Aryzalera detailed description.</t>
+        </is>
+      </c>
       <c r="I33" t="n">
         <v>0</v>
       </c>
@@ -6882,8 +7066,16 @@
           <t>2999763432-795-515966500453</t>
         </is>
       </c>
-      <c r="G34" t="inlineStr"/>
-      <c r="H34" t="inlineStr"/>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ Olcontro</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>Olcontro detailed description.</t>
+        </is>
+      </c>
       <c r="I34" t="n">
         <v>0</v>
       </c>
@@ -7073,8 +7265,16 @@
           <t>4723407051-932-032545262038</t>
         </is>
       </c>
-      <c r="G35" t="inlineStr"/>
-      <c r="H35" t="inlineStr"/>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ Olcontro</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>Olcontro detailed description.</t>
+        </is>
+      </c>
       <c r="I35" t="n">
         <v>0</v>
       </c>
@@ -7268,8 +7468,16 @@
           <t>2858112104-818-001898860054</t>
         </is>
       </c>
-      <c r="G36" t="inlineStr"/>
-      <c r="H36" t="inlineStr"/>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ Attencare</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>Attencare detailed description.</t>
+        </is>
+      </c>
       <c r="I36" t="inlineStr">
         <is>
           <t>APEX PHARMA Saudi</t>
@@ -7461,8 +7669,16 @@
           <t>2417958330-363-094308198090</t>
         </is>
       </c>
-      <c r="G37" t="inlineStr"/>
-      <c r="H37" t="inlineStr"/>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ Attencare</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>Attencare detailed description.</t>
+        </is>
+      </c>
       <c r="I37" t="inlineStr">
         <is>
           <t>APEX PHARMA Saudi</t>
@@ -7650,8 +7866,16 @@
           <t>0858331374-051-975464483255</t>
         </is>
       </c>
-      <c r="G38" t="inlineStr"/>
-      <c r="H38" t="inlineStr"/>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ Attencare</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>Attencare detailed description.</t>
+        </is>
+      </c>
       <c r="I38" t="inlineStr">
         <is>
           <t>APEX PHARMA Saudi</t>
@@ -7843,8 +8067,16 @@
           <t>9602631883-098-833458201040</t>
         </is>
       </c>
-      <c r="G39" t="inlineStr"/>
-      <c r="H39" t="inlineStr"/>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ Attencare</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>Attencare detailed description.</t>
+        </is>
+      </c>
       <c r="I39" t="inlineStr">
         <is>
           <t>APEX PHARMA Saudi</t>
@@ -8032,8 +8264,16 @@
           <t>8724196030-846-903641284113</t>
         </is>
       </c>
-      <c r="G40" t="inlineStr"/>
-      <c r="H40" t="inlineStr"/>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ Attencare</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>Attencare detailed description.</t>
+        </is>
+      </c>
       <c r="I40" t="inlineStr">
         <is>
           <t>APEX PHARMA Saudi</t>
@@ -8225,8 +8465,16 @@
           <t>9054865505-561-850159991198</t>
         </is>
       </c>
-      <c r="G41" t="inlineStr"/>
-      <c r="H41" t="inlineStr"/>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ Iphen</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>Iphen detailed description.</t>
+        </is>
+      </c>
       <c r="I41" t="n">
         <v>0</v>
       </c>
@@ -8607,8 +8855,16 @@
           <t>0749974461-627-426689882512</t>
         </is>
       </c>
-      <c r="G43" t="inlineStr"/>
-      <c r="H43" t="inlineStr"/>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ Vantra</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>Vantra detailed description.</t>
+        </is>
+      </c>
       <c r="I43" t="n">
         <v>0</v>
       </c>
@@ -8794,8 +9050,16 @@
           <t>9487320287-634-934659584206</t>
         </is>
       </c>
-      <c r="G44" t="inlineStr"/>
-      <c r="H44" t="inlineStr"/>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ Vantra</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>Vantra detailed description.</t>
+        </is>
+      </c>
       <c r="I44" t="n">
         <v>0</v>
       </c>
@@ -9176,8 +9440,16 @@
           <t>9917384497-621-072569697017</t>
         </is>
       </c>
-      <c r="G46" t="inlineStr"/>
-      <c r="H46" t="inlineStr"/>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ Ziextenzo</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>Ziextenzo detailed description.</t>
+        </is>
+      </c>
       <c r="I46" t="n">
         <v>0</v>
       </c>
@@ -9375,8 +9647,16 @@
           <t>5742472595-726-820608475018</t>
         </is>
       </c>
-      <c r="G47" t="inlineStr"/>
-      <c r="H47" t="inlineStr"/>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ Rozitta</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>Rozitta detailed description.</t>
+        </is>
+      </c>
       <c r="I47" t="n">
         <v>0</v>
       </c>
@@ -9562,8 +9842,16 @@
           <t>8105026540-695-786266597254</t>
         </is>
       </c>
-      <c r="G48" t="inlineStr"/>
-      <c r="H48" t="inlineStr"/>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ Rozitta</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>Rozitta detailed description.</t>
+        </is>
+      </c>
       <c r="I48" t="n">
         <v>0</v>
       </c>
@@ -12756,8 +13044,16 @@
           <t>6526920190-236-669909012879</t>
         </is>
       </c>
-      <c r="G64" t="inlineStr"/>
-      <c r="H64" t="inlineStr"/>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ ENFORZA</t>
+        </is>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>ENFORZA detailed description.</t>
+        </is>
+      </c>
       <c r="I64" t="n">
         <v>0</v>
       </c>
@@ -13150,8 +13446,16 @@
           <t>1186380634-688-450423170104</t>
         </is>
       </c>
-      <c r="G66" t="inlineStr"/>
-      <c r="H66" t="inlineStr"/>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ OROTIX 120MG F.C.TABLET</t>
+        </is>
+      </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>OROTIX 120MG F.C.TABLET detailed description.</t>
+        </is>
+      </c>
       <c r="I66" t="n">
         <v>0</v>
       </c>
@@ -13942,8 +14246,16 @@
           <t>4125573114-150-025738660970</t>
         </is>
       </c>
-      <c r="G70" t="inlineStr"/>
-      <c r="H70" t="inlineStr"/>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ Xermelo</t>
+        </is>
+      </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>Xermelo detailed description.</t>
+        </is>
+      </c>
       <c r="I70" t="n">
         <v>0</v>
       </c>
@@ -14137,8 +14449,16 @@
           <t>3360253526-544-511679215044</t>
         </is>
       </c>
-      <c r="G71" t="inlineStr"/>
-      <c r="H71" t="inlineStr"/>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ Lovista</t>
+        </is>
+      </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>Lovista detailed description.</t>
+        </is>
+      </c>
       <c r="I71" t="n">
         <v>0</v>
       </c>
@@ -14324,8 +14644,16 @@
           <t>6179466079-105-658423236315</t>
         </is>
       </c>
-      <c r="G72" t="inlineStr"/>
-      <c r="H72" t="inlineStr"/>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ Lovista</t>
+        </is>
+      </c>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>Lovista detailed description.</t>
+        </is>
+      </c>
       <c r="I72" t="n">
         <v>0</v>
       </c>
@@ -14511,8 +14839,16 @@
           <t>6045779275-185-757628001337</t>
         </is>
       </c>
-      <c r="G73" t="inlineStr"/>
-      <c r="H73" t="inlineStr"/>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ Vimpat</t>
+        </is>
+      </c>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>Vimpat detailed description.</t>
+        </is>
+      </c>
       <c r="I73" t="n">
         <v>0</v>
       </c>
@@ -15295,8 +15631,16 @@
           <t>6105679710-272-474914191483</t>
         </is>
       </c>
-      <c r="G77" t="inlineStr"/>
-      <c r="H77" t="inlineStr"/>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ Minoxil</t>
+        </is>
+      </c>
+      <c r="H77" t="inlineStr">
+        <is>
+          <t>Minoxil detailed description.</t>
+        </is>
+      </c>
       <c r="I77" t="n">
         <v>0</v>
       </c>
@@ -15482,8 +15826,16 @@
           <t>4270350123-627-932728906748</t>
         </is>
       </c>
-      <c r="G78" t="inlineStr"/>
-      <c r="H78" t="inlineStr"/>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ Dona</t>
+        </is>
+      </c>
+      <c r="H78" t="inlineStr">
+        <is>
+          <t>Dona detailed description.</t>
+        </is>
+      </c>
       <c r="I78" t="n">
         <v>0</v>
       </c>
@@ -16282,8 +16634,16 @@
           <t>3781725749-131-131596595811</t>
         </is>
       </c>
-      <c r="G82" t="inlineStr"/>
-      <c r="H82" t="inlineStr"/>
+      <c r="G82" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ Rybelsus</t>
+        </is>
+      </c>
+      <c r="H82" t="inlineStr">
+        <is>
+          <t>Rybelsus detailed description.</t>
+        </is>
+      </c>
       <c r="I82" t="n">
         <v>0</v>
       </c>
@@ -16477,8 +16837,16 @@
           <t>8589684229-116-218052203130</t>
         </is>
       </c>
-      <c r="G83" t="inlineStr"/>
-      <c r="H83" t="inlineStr"/>
+      <c r="G83" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ Rybelsus</t>
+        </is>
+      </c>
+      <c r="H83" t="inlineStr">
+        <is>
+          <t>Rybelsus detailed description.</t>
+        </is>
+      </c>
       <c r="I83" t="n">
         <v>0</v>
       </c>
@@ -16668,8 +17036,16 @@
           <t>1716742319-800-501164260747</t>
         </is>
       </c>
-      <c r="G84" t="inlineStr"/>
-      <c r="H84" t="inlineStr"/>
+      <c r="G84" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ Rybelsus</t>
+        </is>
+      </c>
+      <c r="H84" t="inlineStr">
+        <is>
+          <t>Rybelsus detailed description.</t>
+        </is>
+      </c>
       <c r="I84" t="n">
         <v>0</v>
       </c>
@@ -16867,8 +17243,16 @@
           <t>0901612169-577-146138882254</t>
         </is>
       </c>
-      <c r="G85" t="inlineStr"/>
-      <c r="H85" t="inlineStr"/>
+      <c r="G85" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ Bosfit</t>
+        </is>
+      </c>
+      <c r="H85" t="inlineStr">
+        <is>
+          <t>Bosfit detailed description.</t>
+        </is>
+      </c>
       <c r="I85" t="n">
         <v>0</v>
       </c>
@@ -17261,8 +17645,16 @@
           <t>3436875090-166-804753046989</t>
         </is>
       </c>
-      <c r="G87" t="inlineStr"/>
-      <c r="H87" t="inlineStr"/>
+      <c r="G87" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ ESOPOLE</t>
+        </is>
+      </c>
+      <c r="H87" t="inlineStr">
+        <is>
+          <t>ESOPOLE detailed description.</t>
+        </is>
+      </c>
       <c r="I87" t="n">
         <v>0</v>
       </c>
@@ -18256,8 +18648,16 @@
           <t>5229548109-601-054215018084</t>
         </is>
       </c>
-      <c r="G92" t="inlineStr"/>
-      <c r="H92" t="inlineStr"/>
+      <c r="G92" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ Erastapecs Co</t>
+        </is>
+      </c>
+      <c r="H92" t="inlineStr">
+        <is>
+          <t>Erastapecs Co detailed description.</t>
+        </is>
+      </c>
       <c r="I92" t="inlineStr">
         <is>
           <t>APEX PHARMA Saudi</t>
@@ -18449,8 +18849,16 @@
           <t>7425002705-675-188182068018</t>
         </is>
       </c>
-      <c r="G93" t="inlineStr"/>
-      <c r="H93" t="inlineStr"/>
+      <c r="G93" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ Erastapecs Co</t>
+        </is>
+      </c>
+      <c r="H93" t="inlineStr">
+        <is>
+          <t>Erastapecs Co detailed description.</t>
+        </is>
+      </c>
       <c r="I93" t="inlineStr">
         <is>
           <t>APEX PHARMA Saudi</t>
@@ -18638,8 +19046,16 @@
           <t>1568599380-483-009859449973</t>
         </is>
       </c>
-      <c r="G94" t="inlineStr"/>
-      <c r="H94" t="inlineStr"/>
+      <c r="G94" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ Erastapecs Co</t>
+        </is>
+      </c>
+      <c r="H94" t="inlineStr">
+        <is>
+          <t>Erastapecs Co detailed description.</t>
+        </is>
+      </c>
       <c r="I94" t="inlineStr">
         <is>
           <t>APEX PHARMA Saudi</t>
@@ -18827,8 +19243,16 @@
           <t>8419974093-024-058697398562</t>
         </is>
       </c>
-      <c r="G95" t="inlineStr"/>
-      <c r="H95" t="inlineStr"/>
+      <c r="G95" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ TEBARAT</t>
+        </is>
+      </c>
+      <c r="H95" t="inlineStr">
+        <is>
+          <t>TEBARAT detailed description.</t>
+        </is>
+      </c>
       <c r="I95" t="n">
         <v>0</v>
       </c>
@@ -19018,8 +19442,16 @@
           <t>3596875170-571-065342465394</t>
         </is>
       </c>
-      <c r="G96" t="inlineStr"/>
-      <c r="H96" t="inlineStr"/>
+      <c r="G96" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ Coxinix</t>
+        </is>
+      </c>
+      <c r="H96" t="inlineStr">
+        <is>
+          <t>Coxinix detailed description.</t>
+        </is>
+      </c>
       <c r="I96" t="n">
         <v>0</v>
       </c>
@@ -19607,8 +20039,16 @@
           <t>0657865983-311-673502595249</t>
         </is>
       </c>
-      <c r="G99" t="inlineStr"/>
-      <c r="H99" t="inlineStr"/>
+      <c r="G99" t="inlineStr">
+        <is>
+          <t>وصف تفصيلي لـ Abrilada</t>
+        </is>
+      </c>
+      <c r="H99" t="inlineStr">
+        <is>
+          <t>Abrilada detailed description.</t>
+        </is>
+      </c>
       <c r="I99" t="n">
         <v>0</v>
       </c>

--- a/product_upload/packages/46/file.xlsx
+++ b/product_upload/packages/46/file.xlsx
@@ -600,7 +600,7 @@
       </c>
       <c r="AJ1" t="inlineStr">
         <is>
-          <t>Manufacturer Name</t>
+          <t>Manufacturer</t>
         </is>
       </c>
       <c r="AK1" t="inlineStr">
@@ -20674,7 +20674,7 @@
       </c>
       <c r="I1" t="inlineStr">
         <is>
-          <t>Manufacturer Name</t>
+          <t>Manufacturer</t>
         </is>
       </c>
       <c r="J1" t="inlineStr">
@@ -22296,7 +22296,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W21"/>
+  <dimension ref="A1:X21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -22377,40 +22377,45 @@
       </c>
       <c r="P1" t="inlineStr">
         <is>
+          <t>Size unit</t>
+        </is>
+      </c>
+      <c r="Q1" t="inlineStr">
+        <is>
           <t>Manufacturer *</t>
         </is>
       </c>
-      <c r="Q1" t="inlineStr">
+      <c r="R1" t="inlineStr">
         <is>
           <t>price</t>
         </is>
       </c>
-      <c r="R1" t="inlineStr">
+      <c r="S1" t="inlineStr">
         <is>
           <t>Period After Opening.1</t>
         </is>
       </c>
-      <c r="S1" t="inlineStr">
+      <c r="T1" t="inlineStr">
         <is>
           <t>Usage Instructions</t>
         </is>
       </c>
-      <c r="T1" t="inlineStr">
+      <c r="U1" t="inlineStr">
         <is>
           <t>Warnings</t>
         </is>
       </c>
-      <c r="U1" t="inlineStr">
-        <is>
-          <t>Manufacturer Name</t>
-        </is>
-      </c>
       <c r="V1" t="inlineStr">
         <is>
+          <t>Manufacturer</t>
+        </is>
+      </c>
+      <c r="W1" t="inlineStr">
+        <is>
           <t>Ingredients</t>
         </is>
       </c>
-      <c r="W1" t="inlineStr">
+      <c r="X1" t="inlineStr">
         <is>
           <t>Seller SKU</t>
         </is>
@@ -22490,38 +22495,43 @@
       </c>
       <c r="P2" t="inlineStr">
         <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="Q2" t="inlineStr">
+        <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="Q2" t="n">
+      <c r="R2" t="n">
         <v>124.61</v>
       </c>
-      <c r="R2" t="inlineStr">
+      <c r="S2" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="S2" t="inlineStr">
+      <c r="T2" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="T2" t="inlineStr">
+      <c r="U2" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="U2" t="inlineStr">
+      <c r="V2" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="V2" t="inlineStr">
+      <c r="W2" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="W2" t="inlineStr">
+      <c r="X2" t="inlineStr">
         <is>
           <t>SKU-4D84A7801DF2</t>
         </is>
@@ -22601,38 +22611,43 @@
       </c>
       <c r="P3" t="inlineStr">
         <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="Q3" t="inlineStr">
+        <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="Q3" t="n">
+      <c r="R3" t="n">
         <v>492.5</v>
       </c>
-      <c r="R3" t="inlineStr">
+      <c r="S3" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="S3" t="inlineStr">
+      <c r="T3" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="T3" t="inlineStr">
+      <c r="U3" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="U3" t="inlineStr">
+      <c r="V3" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="V3" t="inlineStr">
+      <c r="W3" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="W3" t="inlineStr">
+      <c r="X3" t="inlineStr">
         <is>
           <t>SKU-7D3981EB4DFD</t>
         </is>
@@ -22712,38 +22727,43 @@
       </c>
       <c r="P4" t="inlineStr">
         <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="Q4" t="inlineStr">
+        <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="Q4" t="n">
+      <c r="R4" t="n">
         <v>108.61</v>
       </c>
-      <c r="R4" t="inlineStr">
+      <c r="S4" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="S4" t="inlineStr">
+      <c r="T4" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="T4" t="inlineStr">
+      <c r="U4" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="U4" t="inlineStr">
+      <c r="V4" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="V4" t="inlineStr">
+      <c r="W4" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="W4" t="inlineStr">
+      <c r="X4" t="inlineStr">
         <is>
           <t>SKU-ED3AD3119B91</t>
         </is>
@@ -22823,38 +22843,43 @@
       </c>
       <c r="P5" t="inlineStr">
         <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="Q5" t="inlineStr">
+        <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="Q5" t="n">
+      <c r="R5" t="n">
         <v>270.3</v>
       </c>
-      <c r="R5" t="inlineStr">
+      <c r="S5" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="S5" t="inlineStr">
+      <c r="T5" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="T5" t="inlineStr">
+      <c r="U5" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="U5" t="inlineStr">
+      <c r="V5" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="V5" t="inlineStr">
+      <c r="W5" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="W5" t="inlineStr">
+      <c r="X5" t="inlineStr">
         <is>
           <t>SKU-02643680E63F</t>
         </is>
@@ -22934,38 +22959,43 @@
       </c>
       <c r="P6" t="inlineStr">
         <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="Q6" t="inlineStr">
+        <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="Q6" t="n">
+      <c r="R6" t="n">
         <v>268.9</v>
       </c>
-      <c r="R6" t="inlineStr">
+      <c r="S6" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="S6" t="inlineStr">
+      <c r="T6" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="T6" t="inlineStr">
+      <c r="U6" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="U6" t="inlineStr">
+      <c r="V6" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="V6" t="inlineStr">
+      <c r="W6" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="W6" t="inlineStr">
+      <c r="X6" t="inlineStr">
         <is>
           <t>SKU-0F0ECCC0A873</t>
         </is>
@@ -23045,38 +23075,43 @@
       </c>
       <c r="P7" t="inlineStr">
         <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="Q7" t="inlineStr">
+        <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="Q7" t="n">
+      <c r="R7" t="n">
         <v>251.16</v>
       </c>
-      <c r="R7" t="inlineStr">
+      <c r="S7" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="S7" t="inlineStr">
+      <c r="T7" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="T7" t="inlineStr">
+      <c r="U7" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="U7" t="inlineStr">
+      <c r="V7" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="V7" t="inlineStr">
+      <c r="W7" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="W7" t="inlineStr">
+      <c r="X7" t="inlineStr">
         <is>
           <t>SKU-CAEEDF73C949</t>
         </is>
@@ -23156,38 +23191,43 @@
       </c>
       <c r="P8" t="inlineStr">
         <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="Q8" t="inlineStr">
+        <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="Q8" t="n">
+      <c r="R8" t="n">
         <v>239.45</v>
       </c>
-      <c r="R8" t="inlineStr">
+      <c r="S8" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="S8" t="inlineStr">
+      <c r="T8" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="T8" t="inlineStr">
+      <c r="U8" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="U8" t="inlineStr">
+      <c r="V8" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="V8" t="inlineStr">
+      <c r="W8" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="W8" t="inlineStr">
+      <c r="X8" t="inlineStr">
         <is>
           <t>SKU-68F2D92F6DD1</t>
         </is>
@@ -23267,38 +23307,43 @@
       </c>
       <c r="P9" t="inlineStr">
         <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="Q9" t="inlineStr">
+        <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="Q9" t="n">
+      <c r="R9" t="n">
         <v>486.22</v>
       </c>
-      <c r="R9" t="inlineStr">
+      <c r="S9" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="S9" t="inlineStr">
+      <c r="T9" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="T9" t="inlineStr">
+      <c r="U9" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="U9" t="inlineStr">
+      <c r="V9" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="V9" t="inlineStr">
+      <c r="W9" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="W9" t="inlineStr">
+      <c r="X9" t="inlineStr">
         <is>
           <t>SKU-02BBE68D4F6D</t>
         </is>
@@ -23378,38 +23423,43 @@
       </c>
       <c r="P10" t="inlineStr">
         <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="Q10" t="inlineStr">
+        <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="Q10" t="n">
+      <c r="R10" t="n">
         <v>357.68</v>
       </c>
-      <c r="R10" t="inlineStr">
+      <c r="S10" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="S10" t="inlineStr">
+      <c r="T10" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="T10" t="inlineStr">
+      <c r="U10" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="U10" t="inlineStr">
+      <c r="V10" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="V10" t="inlineStr">
+      <c r="W10" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="W10" t="inlineStr">
+      <c r="X10" t="inlineStr">
         <is>
           <t>SKU-A68FB608CF37</t>
         </is>
@@ -23489,38 +23539,43 @@
       </c>
       <c r="P11" t="inlineStr">
         <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="Q11" t="inlineStr">
+        <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="Q11" t="n">
+      <c r="R11" t="n">
         <v>430.35</v>
       </c>
-      <c r="R11" t="inlineStr">
+      <c r="S11" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="S11" t="inlineStr">
+      <c r="T11" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="T11" t="inlineStr">
+      <c r="U11" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="U11" t="inlineStr">
+      <c r="V11" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="V11" t="inlineStr">
+      <c r="W11" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="W11" t="inlineStr">
+      <c r="X11" t="inlineStr">
         <is>
           <t>SKU-7DB0D2EDB3AF</t>
         </is>
@@ -23600,38 +23655,43 @@
       </c>
       <c r="P12" t="inlineStr">
         <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="Q12" t="inlineStr">
+        <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="Q12" t="n">
+      <c r="R12" t="n">
         <v>130.63</v>
       </c>
-      <c r="R12" t="inlineStr">
+      <c r="S12" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="S12" t="inlineStr">
+      <c r="T12" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="T12" t="inlineStr">
+      <c r="U12" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="U12" t="inlineStr">
+      <c r="V12" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="V12" t="inlineStr">
+      <c r="W12" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="W12" t="inlineStr">
+      <c r="X12" t="inlineStr">
         <is>
           <t>SKU-FB44592CEA6F</t>
         </is>
@@ -23711,38 +23771,43 @@
       </c>
       <c r="P13" t="inlineStr">
         <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="Q13" t="inlineStr">
+        <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="Q13" t="n">
+      <c r="R13" t="n">
         <v>452.27</v>
       </c>
-      <c r="R13" t="inlineStr">
+      <c r="S13" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="S13" t="inlineStr">
+      <c r="T13" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="T13" t="inlineStr">
+      <c r="U13" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="U13" t="inlineStr">
+      <c r="V13" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="V13" t="inlineStr">
+      <c r="W13" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="W13" t="inlineStr">
+      <c r="X13" t="inlineStr">
         <is>
           <t>SKU-4FC2715666EA</t>
         </is>
@@ -23822,38 +23887,43 @@
       </c>
       <c r="P14" t="inlineStr">
         <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="Q14" t="inlineStr">
+        <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="Q14" t="n">
+      <c r="R14" t="n">
         <v>370.13</v>
       </c>
-      <c r="R14" t="inlineStr">
+      <c r="S14" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="S14" t="inlineStr">
+      <c r="T14" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="T14" t="inlineStr">
+      <c r="U14" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="U14" t="inlineStr">
+      <c r="V14" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="V14" t="inlineStr">
+      <c r="W14" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="W14" t="inlineStr">
+      <c r="X14" t="inlineStr">
         <is>
           <t>SKU-B3A3CDA5754A</t>
         </is>
@@ -23933,38 +24003,43 @@
       </c>
       <c r="P15" t="inlineStr">
         <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="Q15" t="inlineStr">
+        <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="Q15" t="n">
+      <c r="R15" t="n">
         <v>22.52</v>
       </c>
-      <c r="R15" t="inlineStr">
+      <c r="S15" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="S15" t="inlineStr">
+      <c r="T15" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="T15" t="inlineStr">
+      <c r="U15" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="U15" t="inlineStr">
+      <c r="V15" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="V15" t="inlineStr">
+      <c r="W15" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="W15" t="inlineStr">
+      <c r="X15" t="inlineStr">
         <is>
           <t>SKU-05C2765669C5</t>
         </is>
@@ -24044,38 +24119,43 @@
       </c>
       <c r="P16" t="inlineStr">
         <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="Q16" t="inlineStr">
+        <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="Q16" t="n">
+      <c r="R16" t="n">
         <v>436.81</v>
       </c>
-      <c r="R16" t="inlineStr">
+      <c r="S16" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="S16" t="inlineStr">
+      <c r="T16" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="T16" t="inlineStr">
+      <c r="U16" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="U16" t="inlineStr">
+      <c r="V16" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="V16" t="inlineStr">
+      <c r="W16" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="W16" t="inlineStr">
+      <c r="X16" t="inlineStr">
         <is>
           <t>SKU-48A97B5F9AA2</t>
         </is>
@@ -24155,38 +24235,43 @@
       </c>
       <c r="P17" t="inlineStr">
         <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="Q17" t="inlineStr">
+        <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="Q17" t="n">
+      <c r="R17" t="n">
         <v>250.85</v>
       </c>
-      <c r="R17" t="inlineStr">
+      <c r="S17" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="S17" t="inlineStr">
+      <c r="T17" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="T17" t="inlineStr">
+      <c r="U17" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="U17" t="inlineStr">
+      <c r="V17" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="V17" t="inlineStr">
+      <c r="W17" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="W17" t="inlineStr">
+      <c r="X17" t="inlineStr">
         <is>
           <t>SKU-5280EA87DFF4</t>
         </is>
@@ -24266,38 +24351,43 @@
       </c>
       <c r="P18" t="inlineStr">
         <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="Q18" t="inlineStr">
+        <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="Q18" t="n">
+      <c r="R18" t="n">
         <v>275.95</v>
       </c>
-      <c r="R18" t="inlineStr">
+      <c r="S18" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="S18" t="inlineStr">
+      <c r="T18" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="T18" t="inlineStr">
+      <c r="U18" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="U18" t="inlineStr">
+      <c r="V18" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="V18" t="inlineStr">
+      <c r="W18" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="W18" t="inlineStr">
+      <c r="X18" t="inlineStr">
         <is>
           <t>SKU-CB8062C2620C</t>
         </is>
@@ -24377,38 +24467,43 @@
       </c>
       <c r="P19" t="inlineStr">
         <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="Q19" t="inlineStr">
+        <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="Q19" t="n">
+      <c r="R19" t="n">
         <v>108.2</v>
       </c>
-      <c r="R19" t="inlineStr">
+      <c r="S19" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="S19" t="inlineStr">
+      <c r="T19" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="T19" t="inlineStr">
+      <c r="U19" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="U19" t="inlineStr">
+      <c r="V19" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="V19" t="inlineStr">
+      <c r="W19" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="W19" t="inlineStr">
+      <c r="X19" t="inlineStr">
         <is>
           <t>SKU-DDA5F16D3EAF</t>
         </is>
@@ -24488,38 +24583,43 @@
       </c>
       <c r="P20" t="inlineStr">
         <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="Q20" t="inlineStr">
+        <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="Q20" t="n">
+      <c r="R20" t="n">
         <v>439.73</v>
       </c>
-      <c r="R20" t="inlineStr">
+      <c r="S20" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="S20" t="inlineStr">
+      <c r="T20" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="T20" t="inlineStr">
+      <c r="U20" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="U20" t="inlineStr">
+      <c r="V20" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="V20" t="inlineStr">
+      <c r="W20" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="W20" t="inlineStr">
+      <c r="X20" t="inlineStr">
         <is>
           <t>SKU-09C077532E92</t>
         </is>
@@ -24599,38 +24699,43 @@
       </c>
       <c r="P21" t="inlineStr">
         <is>
+          <t>ml</t>
+        </is>
+      </c>
+      <c r="Q21" t="inlineStr">
+        <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="Q21" t="n">
+      <c r="R21" t="n">
         <v>164.93</v>
       </c>
-      <c r="R21" t="inlineStr">
+      <c r="S21" t="inlineStr">
         <is>
           <t>12M</t>
         </is>
       </c>
-      <c r="S21" t="inlineStr">
+      <c r="T21" t="inlineStr">
         <is>
           <t>Use as directed</t>
         </is>
       </c>
-      <c r="T21" t="inlineStr">
+      <c r="U21" t="inlineStr">
         <is>
           <t>Keep out of reach of children</t>
         </is>
       </c>
-      <c r="U21" t="inlineStr">
+      <c r="V21" t="inlineStr">
         <is>
           <t>Yusur Pharma</t>
         </is>
       </c>
-      <c r="V21" t="inlineStr">
+      <c r="W21" t="inlineStr">
         <is>
           <t>Aqua, Glycerin</t>
         </is>
       </c>
-      <c r="W21" t="inlineStr">
+      <c r="X21" t="inlineStr">
         <is>
           <t>SKU-A75808CE4D3E</t>
         </is>
